--- a/TMMi ML4 organization assessment by TPI NEXT v1.xlsx
+++ b/TMMi ML4 organization assessment by TPI NEXT v1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VU_MSTH\MSTH Misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1395" documentId="13_ncr:1_{D499AC2A-92F0-485B-91EB-93A176944BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96186801-1F02-44B0-BA40-FE353F928B6C}"/>
+  <xr:revisionPtr revIDLastSave="1400" documentId="13_ncr:1_{D499AC2A-92F0-485B-91EB-93A176944BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1F4D09A-BE2B-47B2-A8D1-3BB124E3C7E9}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="13890" tabRatio="808" firstSheet="16" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -245,7 +245,7 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">PA 4.1 - PA 4.5: GP 2.7. Identify and involve relevant stakeholders.
+      <t xml:space="preserve">PA 4.1 - PA 4.3: GP 2.7. Identify and involve relevant stakeholders.
 </t>
     </r>
     <r>
@@ -11593,7 +11593,7 @@
         <color rgb="FFC65911"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">PA 4.3: SP 2.4. Store data and results. </t>
+      <t xml:space="preserve">PA 4.1: SP 2.4. Store data and results. </t>
     </r>
     <r>
       <rPr>
@@ -11975,7 +11975,7 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">PA 4.1 - PA 4.3: GP 3.2. Collect improvement information.
-PA 4.3: SP 2.4. Store data and results. </t>
+PA 4.1: SP 2.4. Store data and results. </t>
     </r>
     <r>
       <rPr>
@@ -21390,7 +21390,7 @@
     <t>Services in scope and out of scope with regard to test environments are laid down in a Service Catalogue.</t>
   </si>
   <si>
-    <t>Test Maturity Matrix: TMMi maturity level 3 assessment according to TPI NEXT results</t>
+    <t>Test Maturity Matrix: TMMi maturity level 4 assessment according to TPI NEXT results</t>
   </si>
   <si>
     <t>Group</t>
@@ -22659,13 +22659,160 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -22686,44 +22833,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -22734,128 +22845,17 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33626,49 +33626,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="15.75">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="229" t="s">
         <v>613</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
-      <c r="G1" s="164"/>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="164"/>
-      <c r="K1" s="164"/>
-      <c r="L1" s="164"/>
-      <c r="M1" s="164"/>
-      <c r="N1" s="164"/>
-      <c r="O1" s="164"/>
-      <c r="P1" s="164"/>
-      <c r="Q1" s="164"/>
-      <c r="R1" s="164"/>
-      <c r="S1" s="164"/>
-      <c r="T1" s="164"/>
-      <c r="U1" s="164"/>
-      <c r="V1" s="164"/>
-      <c r="W1" s="164"/>
-      <c r="X1" s="164"/>
-      <c r="Y1" s="164"/>
-      <c r="Z1" s="164"/>
-      <c r="AA1" s="164"/>
-      <c r="AB1" s="164"/>
-      <c r="AC1" s="164"/>
-      <c r="AD1" s="164"/>
-      <c r="AE1" s="164"/>
-      <c r="AF1" s="164"/>
-      <c r="AG1" s="164"/>
-      <c r="AH1" s="164"/>
-      <c r="AI1" s="164"/>
-      <c r="AJ1" s="164"/>
-      <c r="AK1" s="164"/>
-      <c r="AL1" s="164"/>
-      <c r="AM1" s="164"/>
-      <c r="AN1" s="164"/>
-      <c r="AO1" s="164"/>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="229"/>
+      <c r="AB1" s="229"/>
+      <c r="AC1" s="229"/>
+      <c r="AD1" s="229"/>
+      <c r="AE1" s="229"/>
+      <c r="AF1" s="229"/>
+      <c r="AG1" s="229"/>
+      <c r="AH1" s="229"/>
+      <c r="AI1" s="229"/>
+      <c r="AJ1" s="229"/>
+      <c r="AK1" s="229"/>
+      <c r="AL1" s="229"/>
+      <c r="AM1" s="229"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="229"/>
     </row>
     <row r="2" spans="1:41">
       <c r="A2" s="141" t="s">
@@ -33683,54 +33683,54 @@
       <c r="D2" s="144" t="s">
         <v>617</v>
       </c>
-      <c r="E2" s="203" t="s">
+      <c r="E2" s="205" t="s">
         <v>618</v>
       </c>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
-      <c r="K2" s="203"/>
-      <c r="L2" s="203"/>
-      <c r="M2" s="203"/>
-      <c r="N2" s="203"/>
-      <c r="O2" s="203"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203" t="s">
+      <c r="F2" s="205"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="205"/>
+      <c r="I2" s="205"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="205"/>
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="205"/>
+      <c r="Q2" s="205" t="s">
         <v>619</v>
       </c>
-      <c r="R2" s="203"/>
-      <c r="S2" s="203"/>
-      <c r="T2" s="203"/>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="203"/>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="203"/>
-      <c r="AA2" s="203"/>
-      <c r="AB2" s="203"/>
-      <c r="AC2" s="203" t="s">
+      <c r="R2" s="205"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="205"/>
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
+      <c r="W2" s="205"/>
+      <c r="X2" s="205"/>
+      <c r="Y2" s="205"/>
+      <c r="Z2" s="205"/>
+      <c r="AA2" s="205"/>
+      <c r="AB2" s="205"/>
+      <c r="AC2" s="205" t="s">
         <v>620</v>
       </c>
-      <c r="AD2" s="203"/>
-      <c r="AE2" s="203"/>
-      <c r="AF2" s="203"/>
-      <c r="AG2" s="203"/>
-      <c r="AH2" s="203"/>
-      <c r="AI2" s="203"/>
-      <c r="AJ2" s="203"/>
-      <c r="AK2" s="203"/>
-      <c r="AL2" s="203"/>
-      <c r="AM2" s="203"/>
-      <c r="AN2" s="203"/>
+      <c r="AD2" s="205"/>
+      <c r="AE2" s="205"/>
+      <c r="AF2" s="205"/>
+      <c r="AG2" s="205"/>
+      <c r="AH2" s="205"/>
+      <c r="AI2" s="205"/>
+      <c r="AJ2" s="205"/>
+      <c r="AK2" s="205"/>
+      <c r="AL2" s="205"/>
+      <c r="AM2" s="205"/>
+      <c r="AN2" s="205"/>
       <c r="AO2" s="145" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:41">
-      <c r="A3" s="228" t="s">
+      <c r="A3" s="164" t="s">
         <v>622</v>
       </c>
       <c r="B3" s="106" t="s">
@@ -33740,68 +33740,68 @@
         <v>624</v>
       </c>
       <c r="D3" s="108"/>
-      <c r="E3" s="210">
+      <c r="E3" s="184">
         <v>1</v>
       </c>
-      <c r="F3" s="211"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="213">
+      <c r="F3" s="185"/>
+      <c r="G3" s="186"/>
+      <c r="H3" s="199">
         <v>2</v>
       </c>
-      <c r="I3" s="214"/>
-      <c r="J3" s="215"/>
-      <c r="K3" s="213">
+      <c r="I3" s="200"/>
+      <c r="J3" s="201"/>
+      <c r="K3" s="199">
         <v>3</v>
       </c>
-      <c r="L3" s="214"/>
-      <c r="M3" s="215"/>
-      <c r="N3" s="213">
+      <c r="L3" s="200"/>
+      <c r="M3" s="201"/>
+      <c r="N3" s="199">
         <v>4</v>
       </c>
-      <c r="O3" s="214"/>
-      <c r="P3" s="215"/>
-      <c r="Q3" s="213">
+      <c r="O3" s="200"/>
+      <c r="P3" s="201"/>
+      <c r="Q3" s="199">
         <v>1</v>
       </c>
-      <c r="R3" s="214"/>
-      <c r="S3" s="214"/>
-      <c r="T3" s="215"/>
-      <c r="U3" s="213">
+      <c r="R3" s="200"/>
+      <c r="S3" s="200"/>
+      <c r="T3" s="201"/>
+      <c r="U3" s="199">
         <v>2</v>
       </c>
-      <c r="V3" s="214"/>
-      <c r="W3" s="214"/>
-      <c r="X3" s="215"/>
-      <c r="Y3" s="210">
+      <c r="V3" s="200"/>
+      <c r="W3" s="200"/>
+      <c r="X3" s="201"/>
+      <c r="Y3" s="184">
         <v>3</v>
       </c>
-      <c r="Z3" s="211"/>
-      <c r="AA3" s="211"/>
-      <c r="AB3" s="212"/>
-      <c r="AC3" s="210">
+      <c r="Z3" s="185"/>
+      <c r="AA3" s="185"/>
+      <c r="AB3" s="186"/>
+      <c r="AC3" s="184">
         <v>1</v>
       </c>
-      <c r="AD3" s="211"/>
-      <c r="AE3" s="211"/>
-      <c r="AF3" s="212"/>
-      <c r="AG3" s="210">
+      <c r="AD3" s="185"/>
+      <c r="AE3" s="185"/>
+      <c r="AF3" s="186"/>
+      <c r="AG3" s="184">
         <v>2</v>
       </c>
-      <c r="AH3" s="211"/>
-      <c r="AI3" s="211"/>
-      <c r="AJ3" s="212"/>
-      <c r="AK3" s="225">
+      <c r="AH3" s="185"/>
+      <c r="AI3" s="185"/>
+      <c r="AJ3" s="186"/>
+      <c r="AK3" s="187">
         <v>3</v>
       </c>
-      <c r="AL3" s="226"/>
-      <c r="AM3" s="226"/>
-      <c r="AN3" s="227"/>
+      <c r="AL3" s="188"/>
+      <c r="AM3" s="188"/>
+      <c r="AN3" s="189"/>
       <c r="AO3" s="109">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:41">
-      <c r="A4" s="229"/>
+      <c r="A4" s="165"/>
       <c r="B4" s="68" t="s">
         <v>625</v>
       </c>
@@ -33809,66 +33809,66 @@
         <v>626</v>
       </c>
       <c r="D4" s="70"/>
-      <c r="E4" s="198">
+      <c r="E4" s="178">
         <v>1</v>
       </c>
-      <c r="F4" s="199"/>
-      <c r="G4" s="200"/>
-      <c r="H4" s="198">
+      <c r="F4" s="179"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="178">
         <v>2</v>
       </c>
-      <c r="I4" s="199"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="204">
+      <c r="I4" s="179"/>
+      <c r="J4" s="180"/>
+      <c r="K4" s="172">
         <v>3</v>
       </c>
-      <c r="L4" s="205"/>
-      <c r="M4" s="206"/>
-      <c r="N4" s="198">
+      <c r="L4" s="173"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="178">
         <v>4</v>
       </c>
-      <c r="O4" s="199"/>
-      <c r="P4" s="200"/>
-      <c r="Q4" s="198">
+      <c r="O4" s="179"/>
+      <c r="P4" s="180"/>
+      <c r="Q4" s="178">
         <v>1</v>
       </c>
-      <c r="R4" s="199"/>
-      <c r="S4" s="199"/>
-      <c r="T4" s="200"/>
-      <c r="U4" s="198">
+      <c r="R4" s="179"/>
+      <c r="S4" s="179"/>
+      <c r="T4" s="180"/>
+      <c r="U4" s="178">
         <v>2</v>
       </c>
-      <c r="V4" s="199"/>
-      <c r="W4" s="199"/>
-      <c r="X4" s="200"/>
-      <c r="Y4" s="204">
+      <c r="V4" s="179"/>
+      <c r="W4" s="179"/>
+      <c r="X4" s="180"/>
+      <c r="Y4" s="172">
         <v>3</v>
       </c>
-      <c r="Z4" s="205"/>
-      <c r="AA4" s="205"/>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="204">
+      <c r="Z4" s="173"/>
+      <c r="AA4" s="173"/>
+      <c r="AB4" s="174"/>
+      <c r="AC4" s="172">
         <v>1</v>
       </c>
-      <c r="AD4" s="205"/>
-      <c r="AE4" s="205"/>
-      <c r="AF4" s="205"/>
-      <c r="AG4" s="205"/>
-      <c r="AH4" s="206"/>
-      <c r="AI4" s="189">
+      <c r="AD4" s="173"/>
+      <c r="AE4" s="173"/>
+      <c r="AF4" s="173"/>
+      <c r="AG4" s="173"/>
+      <c r="AH4" s="174"/>
+      <c r="AI4" s="193">
         <v>2</v>
       </c>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="190"/>
-      <c r="AL4" s="190"/>
-      <c r="AM4" s="190"/>
-      <c r="AN4" s="191"/>
+      <c r="AJ4" s="194"/>
+      <c r="AK4" s="194"/>
+      <c r="AL4" s="194"/>
+      <c r="AM4" s="194"/>
+      <c r="AN4" s="195"/>
       <c r="AO4" s="105">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:41">
-      <c r="A5" s="229"/>
+      <c r="A5" s="165"/>
       <c r="B5" s="68" t="s">
         <v>627</v>
       </c>
@@ -33876,66 +33876,66 @@
         <v>628</v>
       </c>
       <c r="D5" s="70"/>
-      <c r="E5" s="198">
+      <c r="E5" s="178">
         <v>1</v>
       </c>
-      <c r="F5" s="199"/>
-      <c r="G5" s="200"/>
-      <c r="H5" s="198">
+      <c r="F5" s="179"/>
+      <c r="G5" s="180"/>
+      <c r="H5" s="178">
         <v>2</v>
       </c>
-      <c r="I5" s="199"/>
-      <c r="J5" s="200"/>
-      <c r="K5" s="198">
+      <c r="I5" s="179"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="178">
         <v>3</v>
       </c>
-      <c r="L5" s="199"/>
-      <c r="M5" s="200"/>
-      <c r="N5" s="198">
+      <c r="L5" s="179"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="178">
         <v>4</v>
       </c>
-      <c r="O5" s="199"/>
-      <c r="P5" s="200"/>
-      <c r="Q5" s="198">
+      <c r="O5" s="179"/>
+      <c r="P5" s="180"/>
+      <c r="Q5" s="178">
         <v>1</v>
       </c>
-      <c r="R5" s="199"/>
-      <c r="S5" s="199"/>
-      <c r="T5" s="200"/>
-      <c r="U5" s="198">
+      <c r="R5" s="179"/>
+      <c r="S5" s="179"/>
+      <c r="T5" s="180"/>
+      <c r="U5" s="178">
         <v>2</v>
       </c>
-      <c r="V5" s="199"/>
-      <c r="W5" s="199"/>
-      <c r="X5" s="200"/>
-      <c r="Y5" s="198">
+      <c r="V5" s="179"/>
+      <c r="W5" s="179"/>
+      <c r="X5" s="180"/>
+      <c r="Y5" s="178">
         <v>3</v>
       </c>
-      <c r="Z5" s="199"/>
-      <c r="AA5" s="199"/>
-      <c r="AB5" s="200"/>
-      <c r="AC5" s="198">
+      <c r="Z5" s="179"/>
+      <c r="AA5" s="179"/>
+      <c r="AB5" s="180"/>
+      <c r="AC5" s="178">
         <v>1</v>
       </c>
-      <c r="AD5" s="199"/>
-      <c r="AE5" s="199"/>
-      <c r="AF5" s="199"/>
-      <c r="AG5" s="199"/>
-      <c r="AH5" s="200"/>
-      <c r="AI5" s="176">
+      <c r="AD5" s="179"/>
+      <c r="AE5" s="179"/>
+      <c r="AF5" s="179"/>
+      <c r="AG5" s="179"/>
+      <c r="AH5" s="180"/>
+      <c r="AI5" s="190">
         <v>2</v>
       </c>
-      <c r="AJ5" s="177"/>
-      <c r="AK5" s="177"/>
-      <c r="AL5" s="177"/>
-      <c r="AM5" s="177"/>
-      <c r="AN5" s="178"/>
+      <c r="AJ5" s="191"/>
+      <c r="AK5" s="191"/>
+      <c r="AL5" s="191"/>
+      <c r="AM5" s="191"/>
+      <c r="AN5" s="192"/>
       <c r="AO5" s="105">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:41">
-      <c r="A6" s="229"/>
+      <c r="A6" s="165"/>
       <c r="B6" s="68" t="s">
         <v>629</v>
       </c>
@@ -33943,70 +33943,70 @@
         <v>630</v>
       </c>
       <c r="D6" s="70"/>
-      <c r="E6" s="198">
+      <c r="E6" s="178">
         <v>1</v>
       </c>
-      <c r="F6" s="199"/>
-      <c r="G6" s="200"/>
-      <c r="H6" s="198">
+      <c r="F6" s="179"/>
+      <c r="G6" s="180"/>
+      <c r="H6" s="178">
         <v>2</v>
       </c>
-      <c r="I6" s="199"/>
-      <c r="J6" s="200"/>
-      <c r="K6" s="198">
+      <c r="I6" s="179"/>
+      <c r="J6" s="180"/>
+      <c r="K6" s="178">
         <v>3</v>
       </c>
-      <c r="L6" s="199"/>
-      <c r="M6" s="200"/>
-      <c r="N6" s="195">
+      <c r="L6" s="179"/>
+      <c r="M6" s="180"/>
+      <c r="N6" s="169">
         <v>4</v>
       </c>
-      <c r="O6" s="196"/>
-      <c r="P6" s="197"/>
-      <c r="Q6" s="207">
+      <c r="O6" s="170"/>
+      <c r="P6" s="171"/>
+      <c r="Q6" s="181">
         <v>1</v>
       </c>
-      <c r="R6" s="208"/>
-      <c r="S6" s="209"/>
-      <c r="T6" s="204">
+      <c r="R6" s="182"/>
+      <c r="S6" s="183"/>
+      <c r="T6" s="172">
         <v>2</v>
       </c>
-      <c r="U6" s="205"/>
-      <c r="V6" s="206"/>
-      <c r="W6" s="204">
+      <c r="U6" s="173"/>
+      <c r="V6" s="174"/>
+      <c r="W6" s="172">
         <v>3</v>
       </c>
-      <c r="X6" s="205"/>
-      <c r="Y6" s="206"/>
-      <c r="Z6" s="204">
+      <c r="X6" s="173"/>
+      <c r="Y6" s="174"/>
+      <c r="Z6" s="172">
         <v>4</v>
       </c>
-      <c r="AA6" s="205"/>
-      <c r="AB6" s="206"/>
-      <c r="AC6" s="204">
+      <c r="AA6" s="173"/>
+      <c r="AB6" s="174"/>
+      <c r="AC6" s="172">
         <v>1</v>
       </c>
-      <c r="AD6" s="205"/>
-      <c r="AE6" s="205"/>
-      <c r="AF6" s="206"/>
-      <c r="AG6" s="207">
+      <c r="AD6" s="173"/>
+      <c r="AE6" s="173"/>
+      <c r="AF6" s="174"/>
+      <c r="AG6" s="181">
         <v>2</v>
       </c>
-      <c r="AH6" s="208"/>
-      <c r="AI6" s="208"/>
-      <c r="AJ6" s="209"/>
-      <c r="AK6" s="176">
+      <c r="AH6" s="182"/>
+      <c r="AI6" s="182"/>
+      <c r="AJ6" s="183"/>
+      <c r="AK6" s="190">
         <v>3</v>
       </c>
-      <c r="AL6" s="177"/>
-      <c r="AM6" s="177"/>
-      <c r="AN6" s="178"/>
+      <c r="AL6" s="191"/>
+      <c r="AM6" s="191"/>
+      <c r="AN6" s="192"/>
       <c r="AO6" s="105">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:41">
-      <c r="A7" s="229"/>
+      <c r="A7" s="165"/>
       <c r="B7" s="68" t="s">
         <v>631</v>
       </c>
@@ -34014,66 +34014,66 @@
         <v>632</v>
       </c>
       <c r="D7" s="70"/>
-      <c r="E7" s="204">
+      <c r="E7" s="172">
         <v>1</v>
       </c>
-      <c r="F7" s="205"/>
-      <c r="G7" s="206"/>
-      <c r="H7" s="204">
+      <c r="F7" s="173"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="172">
         <v>2</v>
       </c>
-      <c r="I7" s="205"/>
-      <c r="J7" s="206"/>
-      <c r="K7" s="204">
+      <c r="I7" s="173"/>
+      <c r="J7" s="174"/>
+      <c r="K7" s="172">
         <v>3</v>
       </c>
-      <c r="L7" s="205"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="204">
+      <c r="L7" s="173"/>
+      <c r="M7" s="174"/>
+      <c r="N7" s="172">
         <v>4</v>
       </c>
-      <c r="O7" s="205"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="198">
+      <c r="O7" s="173"/>
+      <c r="P7" s="174"/>
+      <c r="Q7" s="178">
         <v>1</v>
       </c>
-      <c r="R7" s="199"/>
-      <c r="S7" s="199"/>
-      <c r="T7" s="200"/>
-      <c r="U7" s="198">
+      <c r="R7" s="179"/>
+      <c r="S7" s="179"/>
+      <c r="T7" s="180"/>
+      <c r="U7" s="178">
         <v>2</v>
       </c>
-      <c r="V7" s="199"/>
-      <c r="W7" s="199"/>
-      <c r="X7" s="200"/>
-      <c r="Y7" s="198">
+      <c r="V7" s="179"/>
+      <c r="W7" s="179"/>
+      <c r="X7" s="180"/>
+      <c r="Y7" s="178">
         <v>3</v>
       </c>
-      <c r="Z7" s="199"/>
-      <c r="AA7" s="199"/>
-      <c r="AB7" s="200"/>
-      <c r="AC7" s="173">
+      <c r="Z7" s="179"/>
+      <c r="AA7" s="179"/>
+      <c r="AB7" s="180"/>
+      <c r="AC7" s="166">
         <v>1</v>
       </c>
-      <c r="AD7" s="174"/>
-      <c r="AE7" s="174"/>
-      <c r="AF7" s="174"/>
-      <c r="AG7" s="174"/>
-      <c r="AH7" s="175"/>
-      <c r="AI7" s="195">
+      <c r="AD7" s="167"/>
+      <c r="AE7" s="167"/>
+      <c r="AF7" s="167"/>
+      <c r="AG7" s="167"/>
+      <c r="AH7" s="168"/>
+      <c r="AI7" s="169">
         <v>2</v>
       </c>
-      <c r="AJ7" s="196"/>
-      <c r="AK7" s="196"/>
-      <c r="AL7" s="196"/>
-      <c r="AM7" s="196"/>
-      <c r="AN7" s="197"/>
+      <c r="AJ7" s="170"/>
+      <c r="AK7" s="170"/>
+      <c r="AL7" s="170"/>
+      <c r="AM7" s="170"/>
+      <c r="AN7" s="171"/>
       <c r="AO7" s="105">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:41">
-      <c r="A8" s="229"/>
+      <c r="A8" s="165"/>
       <c r="B8" s="68" t="s">
         <v>633</v>
       </c>
@@ -34081,64 +34081,64 @@
         <v>634</v>
       </c>
       <c r="D8" s="70"/>
-      <c r="E8" s="198">
+      <c r="E8" s="178">
         <v>1</v>
       </c>
-      <c r="F8" s="199"/>
-      <c r="G8" s="199"/>
-      <c r="H8" s="200"/>
-      <c r="I8" s="198">
+      <c r="F8" s="179"/>
+      <c r="G8" s="179"/>
+      <c r="H8" s="180"/>
+      <c r="I8" s="178">
         <v>2</v>
       </c>
-      <c r="J8" s="199"/>
-      <c r="K8" s="199"/>
-      <c r="L8" s="200"/>
-      <c r="M8" s="198">
+      <c r="J8" s="179"/>
+      <c r="K8" s="179"/>
+      <c r="L8" s="180"/>
+      <c r="M8" s="178">
         <v>3</v>
       </c>
-      <c r="N8" s="199"/>
-      <c r="O8" s="199"/>
-      <c r="P8" s="200"/>
-      <c r="Q8" s="204">
+      <c r="N8" s="179"/>
+      <c r="O8" s="179"/>
+      <c r="P8" s="180"/>
+      <c r="Q8" s="172">
         <v>1</v>
       </c>
-      <c r="R8" s="205"/>
-      <c r="S8" s="205"/>
-      <c r="T8" s="206"/>
-      <c r="U8" s="222">
+      <c r="R8" s="173"/>
+      <c r="S8" s="173"/>
+      <c r="T8" s="174"/>
+      <c r="U8" s="196">
         <v>2</v>
       </c>
-      <c r="V8" s="223"/>
-      <c r="W8" s="223"/>
-      <c r="X8" s="224"/>
-      <c r="Y8" s="222">
+      <c r="V8" s="197"/>
+      <c r="W8" s="197"/>
+      <c r="X8" s="198"/>
+      <c r="Y8" s="196">
         <v>3</v>
       </c>
-      <c r="Z8" s="223"/>
-      <c r="AA8" s="223"/>
-      <c r="AB8" s="224"/>
-      <c r="AC8" s="195">
+      <c r="Z8" s="197"/>
+      <c r="AA8" s="197"/>
+      <c r="AB8" s="198"/>
+      <c r="AC8" s="169">
         <v>1</v>
       </c>
-      <c r="AD8" s="196"/>
-      <c r="AE8" s="196"/>
-      <c r="AF8" s="196"/>
-      <c r="AG8" s="196"/>
-      <c r="AH8" s="197"/>
-      <c r="AI8" s="204">
+      <c r="AD8" s="170"/>
+      <c r="AE8" s="170"/>
+      <c r="AF8" s="170"/>
+      <c r="AG8" s="170"/>
+      <c r="AH8" s="171"/>
+      <c r="AI8" s="172">
         <v>2</v>
       </c>
-      <c r="AJ8" s="205"/>
-      <c r="AK8" s="205"/>
-      <c r="AL8" s="205"/>
-      <c r="AM8" s="205"/>
-      <c r="AN8" s="206"/>
+      <c r="AJ8" s="173"/>
+      <c r="AK8" s="173"/>
+      <c r="AL8" s="173"/>
+      <c r="AM8" s="173"/>
+      <c r="AN8" s="174"/>
       <c r="AO8" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:41">
-      <c r="A9" s="229" t="s">
+      <c r="A9" s="165" t="s">
         <v>635</v>
       </c>
       <c r="B9" s="68" t="s">
@@ -34148,66 +34148,66 @@
         <v>637</v>
       </c>
       <c r="D9" s="70"/>
-      <c r="E9" s="198">
+      <c r="E9" s="178">
         <v>1</v>
       </c>
-      <c r="F9" s="199"/>
-      <c r="G9" s="200"/>
-      <c r="H9" s="198">
+      <c r="F9" s="179"/>
+      <c r="G9" s="180"/>
+      <c r="H9" s="178">
         <v>2</v>
       </c>
-      <c r="I9" s="199"/>
-      <c r="J9" s="200"/>
-      <c r="K9" s="198">
+      <c r="I9" s="179"/>
+      <c r="J9" s="180"/>
+      <c r="K9" s="178">
         <v>3</v>
       </c>
-      <c r="L9" s="199"/>
-      <c r="M9" s="200"/>
-      <c r="N9" s="198">
+      <c r="L9" s="179"/>
+      <c r="M9" s="180"/>
+      <c r="N9" s="178">
         <v>4</v>
       </c>
-      <c r="O9" s="199"/>
-      <c r="P9" s="200"/>
-      <c r="Q9" s="198">
+      <c r="O9" s="179"/>
+      <c r="P9" s="180"/>
+      <c r="Q9" s="178">
         <v>1</v>
       </c>
-      <c r="R9" s="199"/>
-      <c r="S9" s="199"/>
-      <c r="T9" s="200"/>
-      <c r="U9" s="198">
+      <c r="R9" s="179"/>
+      <c r="S9" s="179"/>
+      <c r="T9" s="180"/>
+      <c r="U9" s="178">
         <v>2</v>
       </c>
-      <c r="V9" s="199"/>
-      <c r="W9" s="199"/>
-      <c r="X9" s="200"/>
-      <c r="Y9" s="198">
+      <c r="V9" s="179"/>
+      <c r="W9" s="179"/>
+      <c r="X9" s="180"/>
+      <c r="Y9" s="178">
         <v>3</v>
       </c>
-      <c r="Z9" s="199"/>
-      <c r="AA9" s="199"/>
-      <c r="AB9" s="200"/>
-      <c r="AC9" s="204">
+      <c r="Z9" s="179"/>
+      <c r="AA9" s="179"/>
+      <c r="AB9" s="180"/>
+      <c r="AC9" s="172">
         <v>1</v>
       </c>
-      <c r="AD9" s="205"/>
-      <c r="AE9" s="205"/>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="205"/>
-      <c r="AH9" s="206"/>
-      <c r="AI9" s="204">
+      <c r="AD9" s="173"/>
+      <c r="AE9" s="173"/>
+      <c r="AF9" s="173"/>
+      <c r="AG9" s="173"/>
+      <c r="AH9" s="174"/>
+      <c r="AI9" s="172">
         <v>2</v>
       </c>
-      <c r="AJ9" s="205"/>
-      <c r="AK9" s="205"/>
-      <c r="AL9" s="205"/>
-      <c r="AM9" s="205"/>
-      <c r="AN9" s="206"/>
+      <c r="AJ9" s="173"/>
+      <c r="AK9" s="173"/>
+      <c r="AL9" s="173"/>
+      <c r="AM9" s="173"/>
+      <c r="AN9" s="174"/>
       <c r="AO9" s="109">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:41">
-      <c r="A10" s="229"/>
+      <c r="A10" s="165"/>
       <c r="B10" s="68" t="s">
         <v>638</v>
       </c>
@@ -34215,70 +34215,70 @@
         <v>639</v>
       </c>
       <c r="D10" s="70"/>
-      <c r="E10" s="198">
+      <c r="E10" s="178">
         <v>1</v>
       </c>
-      <c r="F10" s="199"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="198">
+      <c r="F10" s="179"/>
+      <c r="G10" s="180"/>
+      <c r="H10" s="178">
         <v>2</v>
       </c>
-      <c r="I10" s="199"/>
-      <c r="J10" s="200"/>
-      <c r="K10" s="198">
+      <c r="I10" s="179"/>
+      <c r="J10" s="180"/>
+      <c r="K10" s="178">
         <v>3</v>
       </c>
-      <c r="L10" s="199"/>
-      <c r="M10" s="200"/>
-      <c r="N10" s="198">
+      <c r="L10" s="179"/>
+      <c r="M10" s="180"/>
+      <c r="N10" s="178">
         <v>4</v>
       </c>
-      <c r="O10" s="199"/>
-      <c r="P10" s="200"/>
-      <c r="Q10" s="198">
+      <c r="O10" s="179"/>
+      <c r="P10" s="180"/>
+      <c r="Q10" s="178">
         <v>1</v>
       </c>
-      <c r="R10" s="199"/>
-      <c r="S10" s="200"/>
-      <c r="T10" s="198">
+      <c r="R10" s="179"/>
+      <c r="S10" s="180"/>
+      <c r="T10" s="178">
         <v>2</v>
       </c>
-      <c r="U10" s="199"/>
-      <c r="V10" s="200"/>
-      <c r="W10" s="198">
+      <c r="U10" s="179"/>
+      <c r="V10" s="180"/>
+      <c r="W10" s="178">
         <v>3</v>
       </c>
-      <c r="X10" s="199"/>
-      <c r="Y10" s="200"/>
-      <c r="Z10" s="198">
+      <c r="X10" s="179"/>
+      <c r="Y10" s="180"/>
+      <c r="Z10" s="178">
         <v>4</v>
       </c>
-      <c r="AA10" s="199"/>
-      <c r="AB10" s="200"/>
-      <c r="AC10" s="195">
+      <c r="AA10" s="179"/>
+      <c r="AB10" s="180"/>
+      <c r="AC10" s="169">
         <v>1</v>
       </c>
-      <c r="AD10" s="196"/>
-      <c r="AE10" s="196"/>
-      <c r="AF10" s="197"/>
-      <c r="AG10" s="173">
+      <c r="AD10" s="170"/>
+      <c r="AE10" s="170"/>
+      <c r="AF10" s="171"/>
+      <c r="AG10" s="166">
         <v>2</v>
       </c>
-      <c r="AH10" s="174"/>
-      <c r="AI10" s="174"/>
-      <c r="AJ10" s="175"/>
-      <c r="AK10" s="195">
+      <c r="AH10" s="167"/>
+      <c r="AI10" s="167"/>
+      <c r="AJ10" s="168"/>
+      <c r="AK10" s="169">
         <v>3</v>
       </c>
-      <c r="AL10" s="196"/>
-      <c r="AM10" s="196"/>
-      <c r="AN10" s="197"/>
+      <c r="AL10" s="170"/>
+      <c r="AM10" s="170"/>
+      <c r="AN10" s="171"/>
       <c r="AO10" s="105">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:41">
-      <c r="A11" s="229"/>
+      <c r="A11" s="165"/>
       <c r="B11" s="68" t="s">
         <v>640</v>
       </c>
@@ -34286,66 +34286,66 @@
         <v>641</v>
       </c>
       <c r="D11" s="70"/>
-      <c r="E11" s="198">
+      <c r="E11" s="178">
         <v>1</v>
       </c>
-      <c r="F11" s="199"/>
-      <c r="G11" s="199"/>
-      <c r="H11" s="200"/>
-      <c r="I11" s="204">
+      <c r="F11" s="179"/>
+      <c r="G11" s="179"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="172">
         <v>2</v>
       </c>
-      <c r="J11" s="205"/>
-      <c r="K11" s="205"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="198">
+      <c r="J11" s="173"/>
+      <c r="K11" s="173"/>
+      <c r="L11" s="174"/>
+      <c r="M11" s="178">
         <v>3</v>
       </c>
-      <c r="N11" s="199"/>
-      <c r="O11" s="199"/>
-      <c r="P11" s="200"/>
-      <c r="Q11" s="204">
+      <c r="N11" s="179"/>
+      <c r="O11" s="179"/>
+      <c r="P11" s="180"/>
+      <c r="Q11" s="172">
         <v>1</v>
       </c>
-      <c r="R11" s="205"/>
-      <c r="S11" s="206"/>
-      <c r="T11" s="204">
+      <c r="R11" s="173"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="172">
         <v>2</v>
       </c>
-      <c r="U11" s="205"/>
-      <c r="V11" s="206"/>
-      <c r="W11" s="198">
+      <c r="U11" s="173"/>
+      <c r="V11" s="174"/>
+      <c r="W11" s="178">
         <v>3</v>
       </c>
-      <c r="X11" s="199"/>
-      <c r="Y11" s="200"/>
-      <c r="Z11" s="198">
+      <c r="X11" s="179"/>
+      <c r="Y11" s="180"/>
+      <c r="Z11" s="178">
         <v>4</v>
       </c>
-      <c r="AA11" s="199"/>
-      <c r="AB11" s="200"/>
-      <c r="AC11" s="204">
+      <c r="AA11" s="179"/>
+      <c r="AB11" s="180"/>
+      <c r="AC11" s="172">
         <v>1</v>
       </c>
-      <c r="AD11" s="205"/>
-      <c r="AE11" s="205"/>
-      <c r="AF11" s="205"/>
-      <c r="AG11" s="205"/>
-      <c r="AH11" s="206"/>
-      <c r="AI11" s="204">
+      <c r="AD11" s="173"/>
+      <c r="AE11" s="173"/>
+      <c r="AF11" s="173"/>
+      <c r="AG11" s="173"/>
+      <c r="AH11" s="174"/>
+      <c r="AI11" s="172">
         <v>2</v>
       </c>
-      <c r="AJ11" s="205"/>
-      <c r="AK11" s="205"/>
-      <c r="AL11" s="205"/>
-      <c r="AM11" s="205"/>
-      <c r="AN11" s="206"/>
+      <c r="AJ11" s="173"/>
+      <c r="AK11" s="173"/>
+      <c r="AL11" s="173"/>
+      <c r="AM11" s="173"/>
+      <c r="AN11" s="174"/>
       <c r="AO11" s="109">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:41">
-      <c r="A12" s="229"/>
+      <c r="A12" s="165"/>
       <c r="B12" s="68" t="s">
         <v>642</v>
       </c>
@@ -34353,70 +34353,70 @@
         <v>643</v>
       </c>
       <c r="D12" s="70"/>
-      <c r="E12" s="198">
+      <c r="E12" s="178">
         <v>1</v>
       </c>
-      <c r="F12" s="199"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="198">
+      <c r="F12" s="179"/>
+      <c r="G12" s="180"/>
+      <c r="H12" s="178">
         <v>2</v>
       </c>
-      <c r="I12" s="199"/>
-      <c r="J12" s="200"/>
-      <c r="K12" s="198">
+      <c r="I12" s="179"/>
+      <c r="J12" s="180"/>
+      <c r="K12" s="178">
         <v>3</v>
       </c>
-      <c r="L12" s="199"/>
-      <c r="M12" s="200"/>
-      <c r="N12" s="198">
+      <c r="L12" s="179"/>
+      <c r="M12" s="180"/>
+      <c r="N12" s="178">
         <v>4</v>
       </c>
-      <c r="O12" s="199"/>
-      <c r="P12" s="200"/>
-      <c r="Q12" s="198">
+      <c r="O12" s="179"/>
+      <c r="P12" s="180"/>
+      <c r="Q12" s="178">
         <v>1</v>
       </c>
-      <c r="R12" s="199"/>
-      <c r="S12" s="200"/>
-      <c r="T12" s="198">
+      <c r="R12" s="179"/>
+      <c r="S12" s="180"/>
+      <c r="T12" s="178">
         <v>2</v>
       </c>
-      <c r="U12" s="199"/>
-      <c r="V12" s="200"/>
-      <c r="W12" s="219">
+      <c r="U12" s="179"/>
+      <c r="V12" s="180"/>
+      <c r="W12" s="202">
         <v>3</v>
       </c>
-      <c r="X12" s="220"/>
-      <c r="Y12" s="221"/>
-      <c r="Z12" s="198">
+      <c r="X12" s="203"/>
+      <c r="Y12" s="204"/>
+      <c r="Z12" s="178">
         <v>4</v>
       </c>
-      <c r="AA12" s="199"/>
-      <c r="AB12" s="200"/>
-      <c r="AC12" s="198">
+      <c r="AA12" s="179"/>
+      <c r="AB12" s="180"/>
+      <c r="AC12" s="178">
         <v>1</v>
       </c>
-      <c r="AD12" s="199"/>
-      <c r="AE12" s="199"/>
-      <c r="AF12" s="200"/>
-      <c r="AG12" s="207">
+      <c r="AD12" s="179"/>
+      <c r="AE12" s="179"/>
+      <c r="AF12" s="180"/>
+      <c r="AG12" s="181">
         <v>2</v>
       </c>
-      <c r="AH12" s="208"/>
-      <c r="AI12" s="208"/>
-      <c r="AJ12" s="209"/>
-      <c r="AK12" s="195">
+      <c r="AH12" s="182"/>
+      <c r="AI12" s="182"/>
+      <c r="AJ12" s="183"/>
+      <c r="AK12" s="169">
         <v>3</v>
       </c>
-      <c r="AL12" s="196"/>
-      <c r="AM12" s="196"/>
-      <c r="AN12" s="197"/>
+      <c r="AL12" s="170"/>
+      <c r="AM12" s="170"/>
+      <c r="AN12" s="171"/>
       <c r="AO12" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:41">
-      <c r="A13" s="229"/>
+      <c r="A13" s="165"/>
       <c r="B13" s="68" t="s">
         <v>644</v>
       </c>
@@ -34424,68 +34424,68 @@
         <v>645</v>
       </c>
       <c r="D13" s="70"/>
-      <c r="E13" s="198">
+      <c r="E13" s="178">
         <v>1</v>
       </c>
-      <c r="F13" s="199"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="207">
+      <c r="F13" s="179"/>
+      <c r="G13" s="180"/>
+      <c r="H13" s="181">
         <v>2</v>
       </c>
-      <c r="I13" s="208"/>
-      <c r="J13" s="209"/>
-      <c r="K13" s="204">
+      <c r="I13" s="182"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="172">
         <v>3</v>
       </c>
-      <c r="L13" s="205"/>
-      <c r="M13" s="206"/>
-      <c r="N13" s="198">
+      <c r="L13" s="173"/>
+      <c r="M13" s="174"/>
+      <c r="N13" s="178">
         <v>4</v>
       </c>
-      <c r="O13" s="199"/>
-      <c r="P13" s="200"/>
-      <c r="Q13" s="198">
+      <c r="O13" s="179"/>
+      <c r="P13" s="180"/>
+      <c r="Q13" s="178">
         <v>1</v>
       </c>
-      <c r="R13" s="199"/>
-      <c r="S13" s="199"/>
-      <c r="T13" s="200"/>
-      <c r="U13" s="198">
+      <c r="R13" s="179"/>
+      <c r="S13" s="179"/>
+      <c r="T13" s="180"/>
+      <c r="U13" s="178">
         <v>2</v>
       </c>
-      <c r="V13" s="199"/>
-      <c r="W13" s="199"/>
-      <c r="X13" s="200"/>
-      <c r="Y13" s="198">
+      <c r="V13" s="179"/>
+      <c r="W13" s="179"/>
+      <c r="X13" s="180"/>
+      <c r="Y13" s="178">
         <v>3</v>
       </c>
-      <c r="Z13" s="199"/>
-      <c r="AA13" s="199"/>
-      <c r="AB13" s="200"/>
-      <c r="AC13" s="195">
+      <c r="Z13" s="179"/>
+      <c r="AA13" s="179"/>
+      <c r="AB13" s="180"/>
+      <c r="AC13" s="169">
         <v>1</v>
       </c>
-      <c r="AD13" s="196"/>
-      <c r="AE13" s="196"/>
-      <c r="AF13" s="197"/>
-      <c r="AG13" s="204">
+      <c r="AD13" s="170"/>
+      <c r="AE13" s="170"/>
+      <c r="AF13" s="171"/>
+      <c r="AG13" s="172">
         <v>2</v>
       </c>
-      <c r="AH13" s="205"/>
-      <c r="AI13" s="205"/>
-      <c r="AJ13" s="206"/>
-      <c r="AK13" s="204">
+      <c r="AH13" s="173"/>
+      <c r="AI13" s="173"/>
+      <c r="AJ13" s="174"/>
+      <c r="AK13" s="172">
         <v>3</v>
       </c>
-      <c r="AL13" s="205"/>
-      <c r="AM13" s="205"/>
-      <c r="AN13" s="206"/>
+      <c r="AL13" s="173"/>
+      <c r="AM13" s="173"/>
+      <c r="AN13" s="174"/>
       <c r="AO13" s="109">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:41">
-      <c r="A14" s="229" t="s">
+      <c r="A14" s="165" t="s">
         <v>646</v>
       </c>
       <c r="B14" s="68" t="s">
@@ -34495,66 +34495,66 @@
         <v>648</v>
       </c>
       <c r="D14" s="70"/>
-      <c r="E14" s="204">
+      <c r="E14" s="172">
         <v>1</v>
       </c>
-      <c r="F14" s="205"/>
-      <c r="G14" s="205"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="204">
+      <c r="F14" s="173"/>
+      <c r="G14" s="173"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="172">
         <v>2</v>
       </c>
-      <c r="J14" s="205"/>
-      <c r="K14" s="205"/>
-      <c r="L14" s="206"/>
-      <c r="M14" s="204">
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
+      <c r="L14" s="174"/>
+      <c r="M14" s="172">
         <v>3</v>
       </c>
-      <c r="N14" s="205"/>
-      <c r="O14" s="205"/>
-      <c r="P14" s="206"/>
-      <c r="Q14" s="204">
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="174"/>
+      <c r="Q14" s="172">
         <v>1</v>
       </c>
-      <c r="R14" s="205"/>
-      <c r="S14" s="206"/>
-      <c r="T14" s="204">
+      <c r="R14" s="173"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="172">
         <v>2</v>
       </c>
-      <c r="U14" s="205"/>
-      <c r="V14" s="206"/>
-      <c r="W14" s="204">
+      <c r="U14" s="173"/>
+      <c r="V14" s="174"/>
+      <c r="W14" s="172">
         <v>3</v>
       </c>
-      <c r="X14" s="205"/>
-      <c r="Y14" s="206"/>
-      <c r="Z14" s="204">
+      <c r="X14" s="173"/>
+      <c r="Y14" s="174"/>
+      <c r="Z14" s="172">
         <v>4</v>
       </c>
-      <c r="AA14" s="205"/>
-      <c r="AB14" s="206"/>
-      <c r="AC14" s="204">
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="174"/>
+      <c r="AC14" s="172">
         <v>1</v>
       </c>
-      <c r="AD14" s="205"/>
-      <c r="AE14" s="205"/>
-      <c r="AF14" s="205"/>
-      <c r="AG14" s="205"/>
-      <c r="AH14" s="206"/>
-      <c r="AI14" s="204">
+      <c r="AD14" s="173"/>
+      <c r="AE14" s="173"/>
+      <c r="AF14" s="173"/>
+      <c r="AG14" s="173"/>
+      <c r="AH14" s="174"/>
+      <c r="AI14" s="172">
         <v>2</v>
       </c>
-      <c r="AJ14" s="205"/>
-      <c r="AK14" s="205"/>
-      <c r="AL14" s="205"/>
-      <c r="AM14" s="205"/>
-      <c r="AN14" s="206"/>
+      <c r="AJ14" s="173"/>
+      <c r="AK14" s="173"/>
+      <c r="AL14" s="173"/>
+      <c r="AM14" s="173"/>
+      <c r="AN14" s="174"/>
       <c r="AO14" s="109">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:41">
-      <c r="A15" s="229"/>
+      <c r="A15" s="165"/>
       <c r="B15" s="68" t="s">
         <v>649</v>
       </c>
@@ -34562,70 +34562,70 @@
         <v>650</v>
       </c>
       <c r="D15" s="70"/>
-      <c r="E15" s="204">
+      <c r="E15" s="172">
         <v>1</v>
       </c>
-      <c r="F15" s="205"/>
-      <c r="G15" s="206"/>
-      <c r="H15" s="204">
+      <c r="F15" s="173"/>
+      <c r="G15" s="174"/>
+      <c r="H15" s="172">
         <v>2</v>
       </c>
-      <c r="I15" s="205"/>
-      <c r="J15" s="206"/>
-      <c r="K15" s="204">
+      <c r="I15" s="173"/>
+      <c r="J15" s="174"/>
+      <c r="K15" s="172">
         <v>3</v>
       </c>
-      <c r="L15" s="205"/>
-      <c r="M15" s="206"/>
-      <c r="N15" s="204">
+      <c r="L15" s="173"/>
+      <c r="M15" s="174"/>
+      <c r="N15" s="172">
         <v>4</v>
       </c>
-      <c r="O15" s="205"/>
-      <c r="P15" s="206"/>
-      <c r="Q15" s="216">
+      <c r="O15" s="173"/>
+      <c r="P15" s="174"/>
+      <c r="Q15" s="175">
         <v>1</v>
       </c>
-      <c r="R15" s="217"/>
-      <c r="S15" s="218"/>
-      <c r="T15" s="204">
+      <c r="R15" s="176"/>
+      <c r="S15" s="177"/>
+      <c r="T15" s="172">
         <v>2</v>
       </c>
-      <c r="U15" s="205"/>
-      <c r="V15" s="206"/>
-      <c r="W15" s="176">
+      <c r="U15" s="173"/>
+      <c r="V15" s="174"/>
+      <c r="W15" s="190">
         <v>3</v>
       </c>
-      <c r="X15" s="177"/>
-      <c r="Y15" s="178"/>
-      <c r="Z15" s="204">
+      <c r="X15" s="191"/>
+      <c r="Y15" s="192"/>
+      <c r="Z15" s="172">
         <v>4</v>
       </c>
-      <c r="AA15" s="205"/>
-      <c r="AB15" s="206"/>
-      <c r="AC15" s="173">
+      <c r="AA15" s="173"/>
+      <c r="AB15" s="174"/>
+      <c r="AC15" s="166">
         <v>1</v>
       </c>
-      <c r="AD15" s="174"/>
-      <c r="AE15" s="174"/>
-      <c r="AF15" s="175"/>
-      <c r="AG15" s="204">
+      <c r="AD15" s="167"/>
+      <c r="AE15" s="167"/>
+      <c r="AF15" s="168"/>
+      <c r="AG15" s="172">
         <v>2</v>
       </c>
-      <c r="AH15" s="205"/>
-      <c r="AI15" s="205"/>
-      <c r="AJ15" s="206"/>
-      <c r="AK15" s="216">
+      <c r="AH15" s="173"/>
+      <c r="AI15" s="173"/>
+      <c r="AJ15" s="174"/>
+      <c r="AK15" s="175">
         <v>3</v>
       </c>
-      <c r="AL15" s="217"/>
-      <c r="AM15" s="217"/>
-      <c r="AN15" s="218"/>
+      <c r="AL15" s="176"/>
+      <c r="AM15" s="176"/>
+      <c r="AN15" s="177"/>
       <c r="AO15" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:41">
-      <c r="A16" s="229"/>
+      <c r="A16" s="165"/>
       <c r="B16" s="68" t="s">
         <v>651</v>
       </c>
@@ -34633,68 +34633,68 @@
         <v>652</v>
       </c>
       <c r="D16" s="70"/>
-      <c r="E16" s="207">
+      <c r="E16" s="181">
         <v>1</v>
       </c>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="209"/>
-      <c r="I16" s="198">
+      <c r="F16" s="182"/>
+      <c r="G16" s="182"/>
+      <c r="H16" s="183"/>
+      <c r="I16" s="178">
         <v>2</v>
       </c>
-      <c r="J16" s="199"/>
-      <c r="K16" s="199"/>
-      <c r="L16" s="200"/>
-      <c r="M16" s="198">
+      <c r="J16" s="179"/>
+      <c r="K16" s="179"/>
+      <c r="L16" s="180"/>
+      <c r="M16" s="178">
         <v>3</v>
       </c>
-      <c r="N16" s="199"/>
-      <c r="O16" s="199"/>
-      <c r="P16" s="200"/>
-      <c r="Q16" s="207">
+      <c r="N16" s="179"/>
+      <c r="O16" s="179"/>
+      <c r="P16" s="180"/>
+      <c r="Q16" s="181">
         <v>1</v>
       </c>
-      <c r="R16" s="208"/>
-      <c r="S16" s="209"/>
-      <c r="T16" s="198">
+      <c r="R16" s="182"/>
+      <c r="S16" s="183"/>
+      <c r="T16" s="178">
         <v>2</v>
       </c>
-      <c r="U16" s="199"/>
-      <c r="V16" s="200"/>
-      <c r="W16" s="198">
+      <c r="U16" s="179"/>
+      <c r="V16" s="180"/>
+      <c r="W16" s="178">
         <v>3</v>
       </c>
-      <c r="X16" s="199"/>
-      <c r="Y16" s="200"/>
-      <c r="Z16" s="176">
+      <c r="X16" s="179"/>
+      <c r="Y16" s="180"/>
+      <c r="Z16" s="190">
         <v>4</v>
       </c>
-      <c r="AA16" s="177"/>
-      <c r="AB16" s="178"/>
-      <c r="AC16" s="173">
+      <c r="AA16" s="191"/>
+      <c r="AB16" s="192"/>
+      <c r="AC16" s="166">
         <v>1</v>
       </c>
-      <c r="AD16" s="174"/>
-      <c r="AE16" s="174"/>
-      <c r="AF16" s="175"/>
-      <c r="AG16" s="195">
+      <c r="AD16" s="167"/>
+      <c r="AE16" s="167"/>
+      <c r="AF16" s="168"/>
+      <c r="AG16" s="169">
         <v>2</v>
       </c>
-      <c r="AH16" s="196"/>
-      <c r="AI16" s="196"/>
-      <c r="AJ16" s="197"/>
-      <c r="AK16" s="195">
+      <c r="AH16" s="170"/>
+      <c r="AI16" s="170"/>
+      <c r="AJ16" s="171"/>
+      <c r="AK16" s="169">
         <v>3</v>
       </c>
-      <c r="AL16" s="196"/>
-      <c r="AM16" s="196"/>
-      <c r="AN16" s="197"/>
+      <c r="AL16" s="170"/>
+      <c r="AM16" s="170"/>
+      <c r="AN16" s="171"/>
       <c r="AO16" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:43">
-      <c r="A17" s="229"/>
+      <c r="A17" s="165"/>
       <c r="B17" s="68" t="s">
         <v>653</v>
       </c>
@@ -34702,68 +34702,68 @@
         <v>654</v>
       </c>
       <c r="D17" s="70"/>
-      <c r="E17" s="198">
+      <c r="E17" s="178">
         <v>1</v>
       </c>
-      <c r="F17" s="199"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="200"/>
-      <c r="I17" s="198">
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="178">
         <v>2</v>
       </c>
-      <c r="J17" s="199"/>
-      <c r="K17" s="199"/>
-      <c r="L17" s="200"/>
-      <c r="M17" s="204">
+      <c r="J17" s="179"/>
+      <c r="K17" s="179"/>
+      <c r="L17" s="180"/>
+      <c r="M17" s="172">
         <v>3</v>
       </c>
-      <c r="N17" s="205"/>
-      <c r="O17" s="205"/>
-      <c r="P17" s="206"/>
-      <c r="Q17" s="207">
+      <c r="N17" s="173"/>
+      <c r="O17" s="173"/>
+      <c r="P17" s="174"/>
+      <c r="Q17" s="181">
         <v>1</v>
       </c>
-      <c r="R17" s="208"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="207">
+      <c r="R17" s="182"/>
+      <c r="S17" s="183"/>
+      <c r="T17" s="181">
         <v>2</v>
       </c>
-      <c r="U17" s="208"/>
-      <c r="V17" s="209"/>
-      <c r="W17" s="176">
+      <c r="U17" s="182"/>
+      <c r="V17" s="183"/>
+      <c r="W17" s="190">
         <v>3</v>
       </c>
-      <c r="X17" s="177"/>
-      <c r="Y17" s="178"/>
-      <c r="Z17" s="198">
+      <c r="X17" s="191"/>
+      <c r="Y17" s="192"/>
+      <c r="Z17" s="178">
         <v>4</v>
       </c>
-      <c r="AA17" s="199"/>
-      <c r="AB17" s="200"/>
-      <c r="AC17" s="176">
+      <c r="AA17" s="179"/>
+      <c r="AB17" s="180"/>
+      <c r="AC17" s="190">
         <v>1</v>
       </c>
-      <c r="AD17" s="177"/>
-      <c r="AE17" s="177"/>
-      <c r="AF17" s="178"/>
-      <c r="AG17" s="204">
+      <c r="AD17" s="191"/>
+      <c r="AE17" s="191"/>
+      <c r="AF17" s="192"/>
+      <c r="AG17" s="172">
         <v>2</v>
       </c>
-      <c r="AH17" s="205"/>
-      <c r="AI17" s="205"/>
-      <c r="AJ17" s="206"/>
-      <c r="AK17" s="173">
+      <c r="AH17" s="173"/>
+      <c r="AI17" s="173"/>
+      <c r="AJ17" s="174"/>
+      <c r="AK17" s="166">
         <v>3</v>
       </c>
-      <c r="AL17" s="174"/>
-      <c r="AM17" s="174"/>
-      <c r="AN17" s="175"/>
+      <c r="AL17" s="167"/>
+      <c r="AM17" s="167"/>
+      <c r="AN17" s="168"/>
       <c r="AO17" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:43">
-      <c r="A18" s="229"/>
+      <c r="A18" s="165"/>
       <c r="B18" s="68" t="s">
         <v>655</v>
       </c>
@@ -34771,75 +34771,75 @@
         <v>656</v>
       </c>
       <c r="D18" s="70"/>
-      <c r="E18" s="198">
+      <c r="E18" s="178">
         <v>1</v>
       </c>
-      <c r="F18" s="199"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="204">
+      <c r="F18" s="179"/>
+      <c r="G18" s="180"/>
+      <c r="H18" s="172">
         <v>2</v>
       </c>
-      <c r="I18" s="205"/>
-      <c r="J18" s="206"/>
-      <c r="K18" s="198">
+      <c r="I18" s="173"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="178">
         <v>3</v>
       </c>
-      <c r="L18" s="199"/>
-      <c r="M18" s="200"/>
-      <c r="N18" s="207">
+      <c r="L18" s="179"/>
+      <c r="M18" s="180"/>
+      <c r="N18" s="181">
         <v>4</v>
       </c>
-      <c r="O18" s="208"/>
-      <c r="P18" s="209"/>
-      <c r="Q18" s="198">
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="178">
         <v>1</v>
       </c>
-      <c r="R18" s="199"/>
-      <c r="S18" s="200"/>
-      <c r="T18" s="198">
+      <c r="R18" s="179"/>
+      <c r="S18" s="180"/>
+      <c r="T18" s="178">
         <v>2</v>
       </c>
-      <c r="U18" s="199"/>
-      <c r="V18" s="200"/>
-      <c r="W18" s="198">
+      <c r="U18" s="179"/>
+      <c r="V18" s="180"/>
+      <c r="W18" s="178">
         <v>3</v>
       </c>
-      <c r="X18" s="199"/>
-      <c r="Y18" s="200"/>
-      <c r="Z18" s="176">
+      <c r="X18" s="179"/>
+      <c r="Y18" s="180"/>
+      <c r="Z18" s="190">
         <v>4</v>
       </c>
-      <c r="AA18" s="177"/>
-      <c r="AB18" s="178"/>
-      <c r="AC18" s="198">
+      <c r="AA18" s="191"/>
+      <c r="AB18" s="192"/>
+      <c r="AC18" s="178">
         <v>1</v>
       </c>
-      <c r="AD18" s="199"/>
-      <c r="AE18" s="199"/>
-      <c r="AF18" s="200"/>
-      <c r="AG18" s="198">
+      <c r="AD18" s="179"/>
+      <c r="AE18" s="179"/>
+      <c r="AF18" s="180"/>
+      <c r="AG18" s="178">
         <v>2</v>
       </c>
-      <c r="AH18" s="199"/>
-      <c r="AI18" s="199"/>
-      <c r="AJ18" s="200"/>
-      <c r="AK18" s="176">
+      <c r="AH18" s="179"/>
+      <c r="AI18" s="179"/>
+      <c r="AJ18" s="180"/>
+      <c r="AK18" s="190">
         <v>3</v>
       </c>
-      <c r="AL18" s="177"/>
-      <c r="AM18" s="177"/>
-      <c r="AN18" s="178"/>
+      <c r="AL18" s="191"/>
+      <c r="AM18" s="191"/>
+      <c r="AN18" s="192"/>
       <c r="AO18" s="104">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:43">
-      <c r="AK19" s="202" t="s">
+      <c r="AK19" s="207" t="s">
         <v>657</v>
       </c>
-      <c r="AL19" s="202"/>
-      <c r="AM19" s="202"/>
-      <c r="AN19" s="202"/>
+      <c r="AL19" s="207"/>
+      <c r="AM19" s="207"/>
+      <c r="AN19" s="207"/>
     </row>
     <row r="23" spans="1:43" hidden="1"/>
     <row r="24" spans="1:43" hidden="1"/>
@@ -34856,51 +34856,51 @@
       <c r="D25" s="43" t="s">
         <v>658</v>
       </c>
-      <c r="E25" s="201" t="s">
+      <c r="E25" s="206" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="201"/>
-      <c r="G25" s="201"/>
-      <c r="H25" s="201"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="201"/>
-      <c r="K25" s="201"/>
-      <c r="L25" s="201"/>
-      <c r="M25" s="201"/>
-      <c r="N25" s="201"/>
-      <c r="O25" s="201"/>
-      <c r="P25" s="201"/>
-      <c r="Q25" s="201" t="s">
+      <c r="F25" s="206"/>
+      <c r="G25" s="206"/>
+      <c r="H25" s="206"/>
+      <c r="I25" s="206"/>
+      <c r="J25" s="206"/>
+      <c r="K25" s="206"/>
+      <c r="L25" s="206"/>
+      <c r="M25" s="206"/>
+      <c r="N25" s="206"/>
+      <c r="O25" s="206"/>
+      <c r="P25" s="206"/>
+      <c r="Q25" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="R25" s="201"/>
-      <c r="S25" s="201"/>
-      <c r="T25" s="201"/>
-      <c r="U25" s="201"/>
-      <c r="V25" s="201"/>
-      <c r="W25" s="201"/>
-      <c r="X25" s="201"/>
-      <c r="Y25" s="201"/>
-      <c r="Z25" s="201"/>
-      <c r="AA25" s="201"/>
-      <c r="AB25" s="201"/>
-      <c r="AC25" s="201" t="s">
+      <c r="R25" s="206"/>
+      <c r="S25" s="206"/>
+      <c r="T25" s="206"/>
+      <c r="U25" s="206"/>
+      <c r="V25" s="206"/>
+      <c r="W25" s="206"/>
+      <c r="X25" s="206"/>
+      <c r="Y25" s="206"/>
+      <c r="Z25" s="206"/>
+      <c r="AA25" s="206"/>
+      <c r="AB25" s="206"/>
+      <c r="AC25" s="206" t="s">
         <v>659</v>
       </c>
-      <c r="AD25" s="201"/>
-      <c r="AE25" s="201"/>
-      <c r="AF25" s="201"/>
-      <c r="AG25" s="201"/>
-      <c r="AH25" s="201"/>
-      <c r="AI25" s="201"/>
-      <c r="AJ25" s="201"/>
-      <c r="AK25" s="201"/>
-      <c r="AL25" s="201"/>
-      <c r="AM25" s="201"/>
-      <c r="AN25" s="201"/>
+      <c r="AD25" s="206"/>
+      <c r="AE25" s="206"/>
+      <c r="AF25" s="206"/>
+      <c r="AG25" s="206"/>
+      <c r="AH25" s="206"/>
+      <c r="AI25" s="206"/>
+      <c r="AJ25" s="206"/>
+      <c r="AK25" s="206"/>
+      <c r="AL25" s="206"/>
+      <c r="AM25" s="206"/>
+      <c r="AN25" s="206"/>
     </row>
     <row r="26" spans="1:43" hidden="1">
-      <c r="A26" s="183" t="s">
+      <c r="A26" s="208" t="s">
         <v>622</v>
       </c>
       <c r="B26" s="46" t="s">
@@ -34910,62 +34910,62 @@
         <v>624</v>
       </c>
       <c r="D26" s="42"/>
-      <c r="E26" s="180">
+      <c r="E26" s="211">
         <v>0</v>
       </c>
-      <c r="F26" s="180"/>
-      <c r="G26" s="180"/>
-      <c r="H26" s="181">
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="212">
         <v>85</v>
       </c>
-      <c r="I26" s="181"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="181">
+      <c r="I26" s="212"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="212">
         <v>85</v>
       </c>
-      <c r="L26" s="181"/>
-      <c r="M26" s="181"/>
-      <c r="N26" s="181">
+      <c r="L26" s="212"/>
+      <c r="M26" s="212"/>
+      <c r="N26" s="212">
         <v>85</v>
       </c>
-      <c r="O26" s="181"/>
-      <c r="P26" s="181"/>
-      <c r="Q26" s="192">
+      <c r="O26" s="212"/>
+      <c r="P26" s="212"/>
+      <c r="Q26" s="213">
         <v>85</v>
       </c>
-      <c r="R26" s="193"/>
-      <c r="S26" s="193"/>
-      <c r="T26" s="194"/>
-      <c r="U26" s="192">
+      <c r="R26" s="214"/>
+      <c r="S26" s="214"/>
+      <c r="T26" s="215"/>
+      <c r="U26" s="213">
         <v>85</v>
       </c>
-      <c r="V26" s="193"/>
-      <c r="W26" s="193"/>
-      <c r="X26" s="194"/>
-      <c r="Y26" s="167">
+      <c r="V26" s="214"/>
+      <c r="W26" s="214"/>
+      <c r="X26" s="215"/>
+      <c r="Y26" s="216">
         <v>50</v>
       </c>
-      <c r="Z26" s="168"/>
-      <c r="AA26" s="168"/>
-      <c r="AB26" s="169"/>
-      <c r="AC26" s="170">
+      <c r="Z26" s="217"/>
+      <c r="AA26" s="217"/>
+      <c r="AB26" s="218"/>
+      <c r="AC26" s="219">
         <v>0</v>
       </c>
-      <c r="AD26" s="171"/>
-      <c r="AE26" s="171"/>
-      <c r="AF26" s="172"/>
-      <c r="AG26" s="170">
+      <c r="AD26" s="220"/>
+      <c r="AE26" s="220"/>
+      <c r="AF26" s="221"/>
+      <c r="AG26" s="219">
         <v>0</v>
       </c>
-      <c r="AH26" s="171"/>
-      <c r="AI26" s="171"/>
-      <c r="AJ26" s="172"/>
-      <c r="AK26" s="170">
+      <c r="AH26" s="220"/>
+      <c r="AI26" s="220"/>
+      <c r="AJ26" s="221"/>
+      <c r="AK26" s="219">
         <v>0</v>
       </c>
-      <c r="AL26" s="171"/>
-      <c r="AM26" s="171"/>
-      <c r="AN26" s="172"/>
+      <c r="AL26" s="220"/>
+      <c r="AM26" s="220"/>
+      <c r="AN26" s="221"/>
       <c r="AO26">
         <f>SUM(E26:P26)</f>
         <v>255</v>
@@ -34980,7 +34980,7 @@
       </c>
     </row>
     <row r="27" spans="1:43" hidden="1">
-      <c r="A27" s="184"/>
+      <c r="A27" s="209"/>
       <c r="B27" s="46" t="s">
         <v>625</v>
       </c>
@@ -34988,60 +34988,60 @@
         <v>626</v>
       </c>
       <c r="D27" s="42"/>
-      <c r="E27" s="181">
+      <c r="E27" s="212">
         <v>85</v>
       </c>
-      <c r="F27" s="181"/>
-      <c r="G27" s="181"/>
-      <c r="H27" s="165">
+      <c r="F27" s="212"/>
+      <c r="G27" s="212"/>
+      <c r="H27" s="222">
         <v>50</v>
       </c>
-      <c r="I27" s="165"/>
-      <c r="J27" s="165"/>
-      <c r="K27" s="165">
+      <c r="I27" s="222"/>
+      <c r="J27" s="222"/>
+      <c r="K27" s="222">
         <v>50</v>
       </c>
-      <c r="L27" s="165"/>
-      <c r="M27" s="165"/>
-      <c r="N27" s="181">
+      <c r="L27" s="222"/>
+      <c r="M27" s="222"/>
+      <c r="N27" s="212">
         <v>85</v>
       </c>
-      <c r="O27" s="181"/>
-      <c r="P27" s="181"/>
-      <c r="Q27" s="167">
+      <c r="O27" s="212"/>
+      <c r="P27" s="212"/>
+      <c r="Q27" s="216">
         <v>50</v>
       </c>
-      <c r="R27" s="168"/>
-      <c r="S27" s="168"/>
-      <c r="T27" s="169"/>
-      <c r="U27" s="186">
+      <c r="R27" s="217"/>
+      <c r="S27" s="217"/>
+      <c r="T27" s="218"/>
+      <c r="U27" s="223">
         <v>100</v>
       </c>
-      <c r="V27" s="187"/>
-      <c r="W27" s="187"/>
-      <c r="X27" s="188"/>
-      <c r="Y27" s="170">
+      <c r="V27" s="224"/>
+      <c r="W27" s="224"/>
+      <c r="X27" s="225"/>
+      <c r="Y27" s="219">
         <v>0</v>
       </c>
-      <c r="Z27" s="171"/>
-      <c r="AA27" s="171"/>
-      <c r="AB27" s="172"/>
-      <c r="AC27" s="170">
+      <c r="Z27" s="220"/>
+      <c r="AA27" s="220"/>
+      <c r="AB27" s="221"/>
+      <c r="AC27" s="219">
         <v>0</v>
       </c>
-      <c r="AD27" s="171"/>
-      <c r="AE27" s="171"/>
-      <c r="AF27" s="171"/>
-      <c r="AG27" s="171"/>
-      <c r="AH27" s="172"/>
-      <c r="AI27" s="167">
+      <c r="AD27" s="220"/>
+      <c r="AE27" s="220"/>
+      <c r="AF27" s="220"/>
+      <c r="AG27" s="220"/>
+      <c r="AH27" s="221"/>
+      <c r="AI27" s="216">
         <v>50</v>
       </c>
-      <c r="AJ27" s="168"/>
-      <c r="AK27" s="168"/>
-      <c r="AL27" s="168"/>
-      <c r="AM27" s="168"/>
-      <c r="AN27" s="169"/>
+      <c r="AJ27" s="217"/>
+      <c r="AK27" s="217"/>
+      <c r="AL27" s="217"/>
+      <c r="AM27" s="217"/>
+      <c r="AN27" s="218"/>
       <c r="AO27">
         <f t="shared" ref="AO27:AO41" si="0">SUM(E27:P27)</f>
         <v>270</v>
@@ -35056,7 +35056,7 @@
       </c>
     </row>
     <row r="28" spans="1:43" hidden="1">
-      <c r="A28" s="184"/>
+      <c r="A28" s="209"/>
       <c r="B28" s="46" t="s">
         <v>627</v>
       </c>
@@ -35064,60 +35064,60 @@
         <v>628</v>
       </c>
       <c r="D28" s="42"/>
-      <c r="E28" s="181">
+      <c r="E28" s="212">
         <v>85</v>
       </c>
-      <c r="F28" s="181"/>
-      <c r="G28" s="181"/>
-      <c r="H28" s="165">
+      <c r="F28" s="212"/>
+      <c r="G28" s="212"/>
+      <c r="H28" s="222">
         <v>50</v>
       </c>
-      <c r="I28" s="165"/>
-      <c r="J28" s="165"/>
-      <c r="K28" s="165">
+      <c r="I28" s="222"/>
+      <c r="J28" s="222"/>
+      <c r="K28" s="222">
         <v>50</v>
       </c>
-      <c r="L28" s="165"/>
-      <c r="M28" s="165"/>
-      <c r="N28" s="181">
+      <c r="L28" s="222"/>
+      <c r="M28" s="222"/>
+      <c r="N28" s="212">
         <v>85</v>
       </c>
-      <c r="O28" s="181"/>
-      <c r="P28" s="181"/>
-      <c r="Q28" s="192">
+      <c r="O28" s="212"/>
+      <c r="P28" s="212"/>
+      <c r="Q28" s="213">
         <v>85</v>
       </c>
-      <c r="R28" s="193"/>
-      <c r="S28" s="193"/>
-      <c r="T28" s="194"/>
-      <c r="U28" s="167">
+      <c r="R28" s="214"/>
+      <c r="S28" s="214"/>
+      <c r="T28" s="215"/>
+      <c r="U28" s="216">
         <v>50</v>
       </c>
-      <c r="V28" s="168"/>
-      <c r="W28" s="168"/>
-      <c r="X28" s="169"/>
-      <c r="Y28" s="186">
+      <c r="V28" s="217"/>
+      <c r="W28" s="217"/>
+      <c r="X28" s="218"/>
+      <c r="Y28" s="223">
         <v>100</v>
       </c>
-      <c r="Z28" s="187"/>
-      <c r="AA28" s="187"/>
-      <c r="AB28" s="188"/>
-      <c r="AC28" s="167">
+      <c r="Z28" s="224"/>
+      <c r="AA28" s="224"/>
+      <c r="AB28" s="225"/>
+      <c r="AC28" s="216">
         <v>50</v>
       </c>
-      <c r="AD28" s="168"/>
-      <c r="AE28" s="168"/>
-      <c r="AF28" s="168"/>
-      <c r="AG28" s="168"/>
-      <c r="AH28" s="169"/>
-      <c r="AI28" s="170">
+      <c r="AD28" s="217"/>
+      <c r="AE28" s="217"/>
+      <c r="AF28" s="217"/>
+      <c r="AG28" s="217"/>
+      <c r="AH28" s="218"/>
+      <c r="AI28" s="219">
         <v>0</v>
       </c>
-      <c r="AJ28" s="171"/>
-      <c r="AK28" s="171"/>
-      <c r="AL28" s="171"/>
-      <c r="AM28" s="171"/>
-      <c r="AN28" s="172"/>
+      <c r="AJ28" s="220"/>
+      <c r="AK28" s="220"/>
+      <c r="AL28" s="220"/>
+      <c r="AM28" s="220"/>
+      <c r="AN28" s="221"/>
       <c r="AO28">
         <f t="shared" si="0"/>
         <v>270</v>
@@ -35132,7 +35132,7 @@
       </c>
     </row>
     <row r="29" spans="1:43" hidden="1">
-      <c r="A29" s="184"/>
+      <c r="A29" s="209"/>
       <c r="B29" s="46" t="s">
         <v>629</v>
       </c>
@@ -35140,64 +35140,64 @@
         <v>630</v>
       </c>
       <c r="D29" s="42"/>
-      <c r="E29" s="181">
+      <c r="E29" s="212">
         <v>85</v>
       </c>
-      <c r="F29" s="181"/>
-      <c r="G29" s="181"/>
-      <c r="H29" s="165">
+      <c r="F29" s="212"/>
+      <c r="G29" s="212"/>
+      <c r="H29" s="222">
         <v>50</v>
       </c>
-      <c r="I29" s="165"/>
-      <c r="J29" s="165"/>
-      <c r="K29" s="181">
+      <c r="I29" s="222"/>
+      <c r="J29" s="222"/>
+      <c r="K29" s="212">
         <v>85</v>
       </c>
-      <c r="L29" s="181"/>
-      <c r="M29" s="181"/>
-      <c r="N29" s="180">
+      <c r="L29" s="212"/>
+      <c r="M29" s="212"/>
+      <c r="N29" s="211">
         <v>0</v>
       </c>
-      <c r="O29" s="180"/>
-      <c r="P29" s="180"/>
-      <c r="Q29" s="165">
+      <c r="O29" s="211"/>
+      <c r="P29" s="211"/>
+      <c r="Q29" s="222">
         <v>50</v>
       </c>
-      <c r="R29" s="165"/>
-      <c r="S29" s="165"/>
-      <c r="T29" s="181">
+      <c r="R29" s="222"/>
+      <c r="S29" s="222"/>
+      <c r="T29" s="212">
         <v>85</v>
       </c>
-      <c r="U29" s="181"/>
-      <c r="V29" s="181"/>
-      <c r="W29" s="166">
+      <c r="U29" s="212"/>
+      <c r="V29" s="212"/>
+      <c r="W29" s="227">
         <v>0</v>
       </c>
-      <c r="X29" s="166"/>
-      <c r="Y29" s="166"/>
-      <c r="Z29" s="182">
+      <c r="X29" s="227"/>
+      <c r="Y29" s="227"/>
+      <c r="Z29" s="228">
         <v>100</v>
       </c>
-      <c r="AA29" s="182"/>
-      <c r="AB29" s="182"/>
-      <c r="AC29" s="170">
+      <c r="AA29" s="228"/>
+      <c r="AB29" s="228"/>
+      <c r="AC29" s="219">
         <v>0</v>
       </c>
-      <c r="AD29" s="171"/>
-      <c r="AE29" s="171"/>
-      <c r="AF29" s="172"/>
-      <c r="AG29" s="170">
+      <c r="AD29" s="220"/>
+      <c r="AE29" s="220"/>
+      <c r="AF29" s="221"/>
+      <c r="AG29" s="219">
         <v>0</v>
       </c>
-      <c r="AH29" s="171"/>
-      <c r="AI29" s="171"/>
-      <c r="AJ29" s="172"/>
-      <c r="AK29" s="170">
+      <c r="AH29" s="220"/>
+      <c r="AI29" s="220"/>
+      <c r="AJ29" s="221"/>
+      <c r="AK29" s="219">
         <v>0</v>
       </c>
-      <c r="AL29" s="171"/>
-      <c r="AM29" s="171"/>
-      <c r="AN29" s="172"/>
+      <c r="AL29" s="220"/>
+      <c r="AM29" s="220"/>
+      <c r="AN29" s="221"/>
       <c r="AO29">
         <f t="shared" si="0"/>
         <v>220</v>
@@ -35212,7 +35212,7 @@
       </c>
     </row>
     <row r="30" spans="1:43" hidden="1">
-      <c r="A30" s="184"/>
+      <c r="A30" s="209"/>
       <c r="B30" s="46" t="s">
         <v>631</v>
       </c>
@@ -35220,60 +35220,60 @@
         <v>632</v>
       </c>
       <c r="D30" s="42"/>
-      <c r="E30" s="165">
+      <c r="E30" s="222">
         <v>50</v>
       </c>
-      <c r="F30" s="165"/>
-      <c r="G30" s="165"/>
-      <c r="H30" s="179">
+      <c r="F30" s="222"/>
+      <c r="G30" s="222"/>
+      <c r="H30" s="226">
         <v>100</v>
       </c>
-      <c r="I30" s="179"/>
-      <c r="J30" s="179"/>
-      <c r="K30" s="176">
+      <c r="I30" s="226"/>
+      <c r="J30" s="226"/>
+      <c r="K30" s="190">
         <v>0</v>
       </c>
-      <c r="L30" s="177"/>
-      <c r="M30" s="178"/>
-      <c r="N30" s="165">
+      <c r="L30" s="191"/>
+      <c r="M30" s="192"/>
+      <c r="N30" s="222">
         <v>50</v>
       </c>
-      <c r="O30" s="165"/>
-      <c r="P30" s="165"/>
-      <c r="Q30" s="192">
+      <c r="O30" s="222"/>
+      <c r="P30" s="222"/>
+      <c r="Q30" s="213">
         <v>85</v>
       </c>
-      <c r="R30" s="193"/>
-      <c r="S30" s="193"/>
-      <c r="T30" s="194"/>
-      <c r="U30" s="186">
+      <c r="R30" s="214"/>
+      <c r="S30" s="214"/>
+      <c r="T30" s="215"/>
+      <c r="U30" s="223">
         <v>100</v>
       </c>
-      <c r="V30" s="187"/>
-      <c r="W30" s="187"/>
-      <c r="X30" s="188"/>
-      <c r="Y30" s="167">
+      <c r="V30" s="224"/>
+      <c r="W30" s="224"/>
+      <c r="X30" s="225"/>
+      <c r="Y30" s="216">
         <v>50</v>
       </c>
-      <c r="Z30" s="168"/>
-      <c r="AA30" s="168"/>
-      <c r="AB30" s="169"/>
-      <c r="AC30" s="170">
+      <c r="Z30" s="217"/>
+      <c r="AA30" s="217"/>
+      <c r="AB30" s="218"/>
+      <c r="AC30" s="219">
         <v>0</v>
       </c>
-      <c r="AD30" s="171"/>
-      <c r="AE30" s="171"/>
-      <c r="AF30" s="171"/>
-      <c r="AG30" s="171"/>
-      <c r="AH30" s="172"/>
-      <c r="AI30" s="170">
+      <c r="AD30" s="220"/>
+      <c r="AE30" s="220"/>
+      <c r="AF30" s="220"/>
+      <c r="AG30" s="220"/>
+      <c r="AH30" s="221"/>
+      <c r="AI30" s="219">
         <v>0</v>
       </c>
-      <c r="AJ30" s="171"/>
-      <c r="AK30" s="171"/>
-      <c r="AL30" s="171"/>
-      <c r="AM30" s="171"/>
-      <c r="AN30" s="172"/>
+      <c r="AJ30" s="220"/>
+      <c r="AK30" s="220"/>
+      <c r="AL30" s="220"/>
+      <c r="AM30" s="220"/>
+      <c r="AN30" s="221"/>
       <c r="AO30">
         <f t="shared" si="0"/>
         <v>200</v>
@@ -35288,7 +35288,7 @@
       </c>
     </row>
     <row r="31" spans="1:43" hidden="1">
-      <c r="A31" s="185"/>
+      <c r="A31" s="210"/>
       <c r="B31" s="46" t="s">
         <v>633</v>
       </c>
@@ -35296,58 +35296,58 @@
         <v>634</v>
       </c>
       <c r="D31" s="42"/>
-      <c r="E31" s="195">
+      <c r="E31" s="169">
         <v>85</v>
       </c>
-      <c r="F31" s="196"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="197"/>
-      <c r="I31" s="173">
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="171"/>
+      <c r="I31" s="166">
         <v>50</v>
       </c>
-      <c r="J31" s="174"/>
-      <c r="K31" s="174"/>
-      <c r="L31" s="175"/>
-      <c r="M31" s="173">
+      <c r="J31" s="167"/>
+      <c r="K31" s="167"/>
+      <c r="L31" s="168"/>
+      <c r="M31" s="166">
         <v>50</v>
       </c>
-      <c r="N31" s="174"/>
-      <c r="O31" s="174"/>
-      <c r="P31" s="175"/>
-      <c r="Q31" s="170">
+      <c r="N31" s="167"/>
+      <c r="O31" s="167"/>
+      <c r="P31" s="168"/>
+      <c r="Q31" s="219">
         <v>0</v>
       </c>
-      <c r="R31" s="171"/>
-      <c r="S31" s="171"/>
-      <c r="T31" s="172"/>
-      <c r="U31" s="167">
+      <c r="R31" s="220"/>
+      <c r="S31" s="220"/>
+      <c r="T31" s="221"/>
+      <c r="U31" s="216">
         <v>50</v>
       </c>
-      <c r="V31" s="168"/>
-      <c r="W31" s="168"/>
-      <c r="X31" s="169"/>
-      <c r="Y31" s="167">
+      <c r="V31" s="217"/>
+      <c r="W31" s="217"/>
+      <c r="X31" s="218"/>
+      <c r="Y31" s="216">
         <v>50</v>
       </c>
-      <c r="Z31" s="168"/>
-      <c r="AA31" s="168"/>
-      <c r="AB31" s="169"/>
-      <c r="AC31" s="170">
+      <c r="Z31" s="217"/>
+      <c r="AA31" s="217"/>
+      <c r="AB31" s="218"/>
+      <c r="AC31" s="219">
         <v>0</v>
       </c>
-      <c r="AD31" s="171"/>
-      <c r="AE31" s="171"/>
-      <c r="AF31" s="171"/>
-      <c r="AG31" s="171"/>
-      <c r="AH31" s="172"/>
-      <c r="AI31" s="170">
+      <c r="AD31" s="220"/>
+      <c r="AE31" s="220"/>
+      <c r="AF31" s="220"/>
+      <c r="AG31" s="220"/>
+      <c r="AH31" s="221"/>
+      <c r="AI31" s="219">
         <v>0</v>
       </c>
-      <c r="AJ31" s="171"/>
-      <c r="AK31" s="171"/>
-      <c r="AL31" s="171"/>
-      <c r="AM31" s="171"/>
-      <c r="AN31" s="172"/>
+      <c r="AJ31" s="220"/>
+      <c r="AK31" s="220"/>
+      <c r="AL31" s="220"/>
+      <c r="AM31" s="220"/>
+      <c r="AN31" s="221"/>
       <c r="AO31">
         <f t="shared" si="0"/>
         <v>185</v>
@@ -35362,7 +35362,7 @@
       </c>
     </row>
     <row r="32" spans="1:43" hidden="1">
-      <c r="A32" s="183" t="s">
+      <c r="A32" s="208" t="s">
         <v>635</v>
       </c>
       <c r="B32" s="46" t="s">
@@ -35372,60 +35372,60 @@
         <v>637</v>
       </c>
       <c r="D32" s="42"/>
-      <c r="E32" s="181">
+      <c r="E32" s="212">
         <v>85</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="165">
+      <c r="F32" s="212"/>
+      <c r="G32" s="212"/>
+      <c r="H32" s="222">
         <v>50</v>
       </c>
-      <c r="I32" s="165"/>
-      <c r="J32" s="165"/>
-      <c r="K32" s="181">
+      <c r="I32" s="222"/>
+      <c r="J32" s="222"/>
+      <c r="K32" s="212">
         <v>85</v>
       </c>
-      <c r="L32" s="181"/>
-      <c r="M32" s="181"/>
-      <c r="N32" s="179">
+      <c r="L32" s="212"/>
+      <c r="M32" s="212"/>
+      <c r="N32" s="226">
         <v>100</v>
       </c>
-      <c r="O32" s="179"/>
-      <c r="P32" s="179"/>
-      <c r="Q32" s="192">
+      <c r="O32" s="226"/>
+      <c r="P32" s="226"/>
+      <c r="Q32" s="213">
         <v>85</v>
       </c>
-      <c r="R32" s="193"/>
-      <c r="S32" s="193"/>
-      <c r="T32" s="194"/>
-      <c r="U32" s="186">
+      <c r="R32" s="214"/>
+      <c r="S32" s="214"/>
+      <c r="T32" s="215"/>
+      <c r="U32" s="223">
         <v>100</v>
       </c>
-      <c r="V32" s="187"/>
-      <c r="W32" s="187"/>
-      <c r="X32" s="188"/>
-      <c r="Y32" s="167">
+      <c r="V32" s="224"/>
+      <c r="W32" s="224"/>
+      <c r="X32" s="225"/>
+      <c r="Y32" s="216">
         <v>50</v>
       </c>
-      <c r="Z32" s="168"/>
-      <c r="AA32" s="168"/>
-      <c r="AB32" s="169"/>
-      <c r="AC32" s="192">
+      <c r="Z32" s="217"/>
+      <c r="AA32" s="217"/>
+      <c r="AB32" s="218"/>
+      <c r="AC32" s="213">
         <v>85</v>
       </c>
-      <c r="AD32" s="193"/>
-      <c r="AE32" s="193"/>
-      <c r="AF32" s="193"/>
-      <c r="AG32" s="193"/>
-      <c r="AH32" s="194"/>
-      <c r="AI32" s="170">
+      <c r="AD32" s="214"/>
+      <c r="AE32" s="214"/>
+      <c r="AF32" s="214"/>
+      <c r="AG32" s="214"/>
+      <c r="AH32" s="215"/>
+      <c r="AI32" s="219">
         <v>0</v>
       </c>
-      <c r="AJ32" s="171"/>
-      <c r="AK32" s="171"/>
-      <c r="AL32" s="171"/>
-      <c r="AM32" s="171"/>
-      <c r="AN32" s="172"/>
+      <c r="AJ32" s="220"/>
+      <c r="AK32" s="220"/>
+      <c r="AL32" s="220"/>
+      <c r="AM32" s="220"/>
+      <c r="AN32" s="221"/>
       <c r="AO32">
         <f t="shared" si="0"/>
         <v>320</v>
@@ -35440,7 +35440,7 @@
       </c>
     </row>
     <row r="33" spans="1:43" hidden="1">
-      <c r="A33" s="184"/>
+      <c r="A33" s="209"/>
       <c r="B33" s="46" t="s">
         <v>638</v>
       </c>
@@ -35448,64 +35448,64 @@
         <v>639</v>
       </c>
       <c r="D33" s="42"/>
-      <c r="E33" s="179">
+      <c r="E33" s="226">
         <v>100</v>
       </c>
-      <c r="F33" s="179"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="179">
+      <c r="F33" s="226"/>
+      <c r="G33" s="226"/>
+      <c r="H33" s="226">
         <v>100</v>
       </c>
-      <c r="I33" s="179"/>
-      <c r="J33" s="179"/>
-      <c r="K33" s="165">
+      <c r="I33" s="226"/>
+      <c r="J33" s="226"/>
+      <c r="K33" s="222">
         <v>50</v>
       </c>
-      <c r="L33" s="165"/>
-      <c r="M33" s="165"/>
-      <c r="N33" s="181">
+      <c r="L33" s="222"/>
+      <c r="M33" s="222"/>
+      <c r="N33" s="212">
         <v>85</v>
       </c>
-      <c r="O33" s="181"/>
-      <c r="P33" s="181"/>
-      <c r="Q33" s="165">
+      <c r="O33" s="212"/>
+      <c r="P33" s="212"/>
+      <c r="Q33" s="222">
         <v>50</v>
       </c>
-      <c r="R33" s="165"/>
-      <c r="S33" s="165"/>
-      <c r="T33" s="181">
+      <c r="R33" s="222"/>
+      <c r="S33" s="222"/>
+      <c r="T33" s="212">
         <v>85</v>
       </c>
-      <c r="U33" s="181"/>
-      <c r="V33" s="181"/>
-      <c r="W33" s="165">
+      <c r="U33" s="212"/>
+      <c r="V33" s="212"/>
+      <c r="W33" s="222">
         <v>50</v>
       </c>
-      <c r="X33" s="165"/>
-      <c r="Y33" s="165"/>
-      <c r="Z33" s="165">
+      <c r="X33" s="222"/>
+      <c r="Y33" s="222"/>
+      <c r="Z33" s="222">
         <v>50</v>
       </c>
-      <c r="AA33" s="165"/>
-      <c r="AB33" s="165"/>
-      <c r="AC33" s="170">
+      <c r="AA33" s="222"/>
+      <c r="AB33" s="222"/>
+      <c r="AC33" s="219">
         <v>0</v>
       </c>
-      <c r="AD33" s="171"/>
-      <c r="AE33" s="171"/>
-      <c r="AF33" s="172"/>
-      <c r="AG33" s="170">
+      <c r="AD33" s="220"/>
+      <c r="AE33" s="220"/>
+      <c r="AF33" s="221"/>
+      <c r="AG33" s="219">
         <v>0</v>
       </c>
-      <c r="AH33" s="171"/>
-      <c r="AI33" s="171"/>
-      <c r="AJ33" s="172"/>
-      <c r="AK33" s="170">
+      <c r="AH33" s="220"/>
+      <c r="AI33" s="220"/>
+      <c r="AJ33" s="221"/>
+      <c r="AK33" s="219">
         <v>0</v>
       </c>
-      <c r="AL33" s="171"/>
-      <c r="AM33" s="171"/>
-      <c r="AN33" s="172"/>
+      <c r="AL33" s="220"/>
+      <c r="AM33" s="220"/>
+      <c r="AN33" s="221"/>
       <c r="AO33">
         <f t="shared" si="0"/>
         <v>335</v>
@@ -35520,7 +35520,7 @@
       </c>
     </row>
     <row r="34" spans="1:43" hidden="1">
-      <c r="A34" s="184"/>
+      <c r="A34" s="209"/>
       <c r="B34" s="46" t="s">
         <v>640</v>
       </c>
@@ -35528,60 +35528,60 @@
         <v>641</v>
       </c>
       <c r="D34" s="42"/>
-      <c r="E34" s="176">
+      <c r="E34" s="190">
         <v>0</v>
       </c>
-      <c r="F34" s="177"/>
-      <c r="G34" s="177"/>
-      <c r="H34" s="178"/>
-      <c r="I34" s="176">
+      <c r="F34" s="191"/>
+      <c r="G34" s="191"/>
+      <c r="H34" s="192"/>
+      <c r="I34" s="190">
         <v>0</v>
       </c>
-      <c r="J34" s="177"/>
-      <c r="K34" s="177"/>
-      <c r="L34" s="178"/>
-      <c r="M34" s="176">
+      <c r="J34" s="191"/>
+      <c r="K34" s="191"/>
+      <c r="L34" s="192"/>
+      <c r="M34" s="190">
         <v>0</v>
       </c>
-      <c r="N34" s="177"/>
-      <c r="O34" s="177"/>
-      <c r="P34" s="178"/>
-      <c r="Q34" s="166">
+      <c r="N34" s="191"/>
+      <c r="O34" s="191"/>
+      <c r="P34" s="192"/>
+      <c r="Q34" s="227">
         <v>0</v>
       </c>
-      <c r="R34" s="166"/>
-      <c r="S34" s="166"/>
-      <c r="T34" s="166">
+      <c r="R34" s="227"/>
+      <c r="S34" s="227"/>
+      <c r="T34" s="227">
         <v>0</v>
       </c>
-      <c r="U34" s="166"/>
-      <c r="V34" s="166"/>
-      <c r="W34" s="166">
+      <c r="U34" s="227"/>
+      <c r="V34" s="227"/>
+      <c r="W34" s="227">
         <v>0</v>
       </c>
-      <c r="X34" s="166"/>
-      <c r="Y34" s="166"/>
-      <c r="Z34" s="166">
+      <c r="X34" s="227"/>
+      <c r="Y34" s="227"/>
+      <c r="Z34" s="227">
         <v>0</v>
       </c>
-      <c r="AA34" s="166"/>
-      <c r="AB34" s="166"/>
-      <c r="AC34" s="170">
+      <c r="AA34" s="227"/>
+      <c r="AB34" s="227"/>
+      <c r="AC34" s="219">
         <v>0</v>
       </c>
-      <c r="AD34" s="171"/>
-      <c r="AE34" s="171"/>
-      <c r="AF34" s="171"/>
-      <c r="AG34" s="171"/>
-      <c r="AH34" s="172"/>
-      <c r="AI34" s="170">
+      <c r="AD34" s="220"/>
+      <c r="AE34" s="220"/>
+      <c r="AF34" s="220"/>
+      <c r="AG34" s="220"/>
+      <c r="AH34" s="221"/>
+      <c r="AI34" s="219">
         <v>0</v>
       </c>
-      <c r="AJ34" s="171"/>
-      <c r="AK34" s="171"/>
-      <c r="AL34" s="171"/>
-      <c r="AM34" s="171"/>
-      <c r="AN34" s="172"/>
+      <c r="AJ34" s="220"/>
+      <c r="AK34" s="220"/>
+      <c r="AL34" s="220"/>
+      <c r="AM34" s="220"/>
+      <c r="AN34" s="221"/>
       <c r="AO34">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -35596,7 +35596,7 @@
       </c>
     </row>
     <row r="35" spans="1:43" hidden="1">
-      <c r="A35" s="184"/>
+      <c r="A35" s="209"/>
       <c r="B35" s="46" t="s">
         <v>642</v>
       </c>
@@ -35604,64 +35604,64 @@
         <v>643</v>
       </c>
       <c r="D35" s="42"/>
-      <c r="E35" s="181">
+      <c r="E35" s="212">
         <v>85</v>
       </c>
-      <c r="F35" s="181"/>
-      <c r="G35" s="181"/>
-      <c r="H35" s="181">
+      <c r="F35" s="212"/>
+      <c r="G35" s="212"/>
+      <c r="H35" s="212">
         <v>85</v>
       </c>
-      <c r="I35" s="181"/>
-      <c r="J35" s="181"/>
-      <c r="K35" s="179">
+      <c r="I35" s="212"/>
+      <c r="J35" s="212"/>
+      <c r="K35" s="226">
         <v>100</v>
       </c>
-      <c r="L35" s="179"/>
-      <c r="M35" s="179"/>
-      <c r="N35" s="165">
+      <c r="L35" s="226"/>
+      <c r="M35" s="226"/>
+      <c r="N35" s="222">
         <v>50</v>
       </c>
-      <c r="O35" s="165"/>
-      <c r="P35" s="165"/>
-      <c r="Q35" s="165">
+      <c r="O35" s="222"/>
+      <c r="P35" s="222"/>
+      <c r="Q35" s="222">
         <v>50</v>
       </c>
-      <c r="R35" s="165"/>
-      <c r="S35" s="165"/>
-      <c r="T35" s="165">
+      <c r="R35" s="222"/>
+      <c r="S35" s="222"/>
+      <c r="T35" s="222">
         <v>50</v>
       </c>
-      <c r="U35" s="165"/>
-      <c r="V35" s="165"/>
-      <c r="W35" s="181">
+      <c r="U35" s="222"/>
+      <c r="V35" s="222"/>
+      <c r="W35" s="212">
         <v>85</v>
       </c>
-      <c r="X35" s="181"/>
-      <c r="Y35" s="181"/>
-      <c r="Z35" s="165">
+      <c r="X35" s="212"/>
+      <c r="Y35" s="212"/>
+      <c r="Z35" s="222">
         <v>50</v>
       </c>
-      <c r="AA35" s="165"/>
-      <c r="AB35" s="165"/>
-      <c r="AC35" s="192">
+      <c r="AA35" s="222"/>
+      <c r="AB35" s="222"/>
+      <c r="AC35" s="213">
         <v>85</v>
       </c>
-      <c r="AD35" s="193"/>
-      <c r="AE35" s="193"/>
-      <c r="AF35" s="194"/>
-      <c r="AG35" s="192">
+      <c r="AD35" s="214"/>
+      <c r="AE35" s="214"/>
+      <c r="AF35" s="215"/>
+      <c r="AG35" s="213">
         <v>85</v>
       </c>
-      <c r="AH35" s="193"/>
-      <c r="AI35" s="193"/>
-      <c r="AJ35" s="194"/>
-      <c r="AK35" s="170">
+      <c r="AH35" s="214"/>
+      <c r="AI35" s="214"/>
+      <c r="AJ35" s="215"/>
+      <c r="AK35" s="219">
         <v>0</v>
       </c>
-      <c r="AL35" s="171"/>
-      <c r="AM35" s="171"/>
-      <c r="AN35" s="172"/>
+      <c r="AL35" s="220"/>
+      <c r="AM35" s="220"/>
+      <c r="AN35" s="221"/>
       <c r="AO35">
         <f t="shared" si="0"/>
         <v>320</v>
@@ -35676,7 +35676,7 @@
       </c>
     </row>
     <row r="36" spans="1:43" hidden="1">
-      <c r="A36" s="185"/>
+      <c r="A36" s="210"/>
       <c r="B36" s="46" t="s">
         <v>644</v>
       </c>
@@ -35684,62 +35684,62 @@
         <v>645</v>
       </c>
       <c r="D36" s="42"/>
-      <c r="E36" s="165">
+      <c r="E36" s="222">
         <v>50</v>
       </c>
-      <c r="F36" s="165"/>
-      <c r="G36" s="165"/>
-      <c r="H36" s="181">
+      <c r="F36" s="222"/>
+      <c r="G36" s="222"/>
+      <c r="H36" s="212">
         <v>85</v>
       </c>
-      <c r="I36" s="181"/>
-      <c r="J36" s="181"/>
-      <c r="K36" s="165">
+      <c r="I36" s="212"/>
+      <c r="J36" s="212"/>
+      <c r="K36" s="222">
         <v>50</v>
       </c>
-      <c r="L36" s="165"/>
-      <c r="M36" s="165"/>
-      <c r="N36" s="180">
+      <c r="L36" s="222"/>
+      <c r="M36" s="222"/>
+      <c r="N36" s="211">
         <v>0</v>
       </c>
-      <c r="O36" s="180"/>
-      <c r="P36" s="180"/>
-      <c r="Q36" s="167">
+      <c r="O36" s="211"/>
+      <c r="P36" s="211"/>
+      <c r="Q36" s="216">
         <v>50</v>
       </c>
-      <c r="R36" s="168"/>
-      <c r="S36" s="168"/>
-      <c r="T36" s="169"/>
-      <c r="U36" s="186">
+      <c r="R36" s="217"/>
+      <c r="S36" s="217"/>
+      <c r="T36" s="218"/>
+      <c r="U36" s="223">
         <v>100</v>
       </c>
-      <c r="V36" s="187"/>
-      <c r="W36" s="187"/>
-      <c r="X36" s="188"/>
-      <c r="Y36" s="167">
+      <c r="V36" s="224"/>
+      <c r="W36" s="224"/>
+      <c r="X36" s="225"/>
+      <c r="Y36" s="216">
         <v>50</v>
       </c>
-      <c r="Z36" s="168"/>
-      <c r="AA36" s="168"/>
-      <c r="AB36" s="169"/>
-      <c r="AC36" s="167">
+      <c r="Z36" s="217"/>
+      <c r="AA36" s="217"/>
+      <c r="AB36" s="218"/>
+      <c r="AC36" s="216">
         <v>50</v>
       </c>
-      <c r="AD36" s="168"/>
-      <c r="AE36" s="168"/>
-      <c r="AF36" s="169"/>
-      <c r="AG36" s="170">
+      <c r="AD36" s="217"/>
+      <c r="AE36" s="217"/>
+      <c r="AF36" s="218"/>
+      <c r="AG36" s="219">
         <v>0</v>
       </c>
-      <c r="AH36" s="171"/>
-      <c r="AI36" s="171"/>
-      <c r="AJ36" s="172"/>
-      <c r="AK36" s="170">
+      <c r="AH36" s="220"/>
+      <c r="AI36" s="220"/>
+      <c r="AJ36" s="221"/>
+      <c r="AK36" s="219">
         <v>0</v>
       </c>
-      <c r="AL36" s="171"/>
-      <c r="AM36" s="171"/>
-      <c r="AN36" s="172"/>
+      <c r="AL36" s="220"/>
+      <c r="AM36" s="220"/>
+      <c r="AN36" s="221"/>
       <c r="AO36">
         <f t="shared" si="0"/>
         <v>185</v>
@@ -35754,7 +35754,7 @@
       </c>
     </row>
     <row r="37" spans="1:43" hidden="1">
-      <c r="A37" s="183" t="s">
+      <c r="A37" s="208" t="s">
         <v>646</v>
       </c>
       <c r="B37" s="46" t="s">
@@ -35764,60 +35764,60 @@
         <v>648</v>
       </c>
       <c r="D37" s="42"/>
-      <c r="E37" s="176">
+      <c r="E37" s="190">
         <v>0</v>
       </c>
-      <c r="F37" s="177"/>
-      <c r="G37" s="177"/>
-      <c r="H37" s="178"/>
-      <c r="I37" s="176">
+      <c r="F37" s="191"/>
+      <c r="G37" s="191"/>
+      <c r="H37" s="192"/>
+      <c r="I37" s="190">
         <v>0</v>
       </c>
-      <c r="J37" s="177"/>
-      <c r="K37" s="177"/>
-      <c r="L37" s="178"/>
-      <c r="M37" s="176">
+      <c r="J37" s="191"/>
+      <c r="K37" s="191"/>
+      <c r="L37" s="192"/>
+      <c r="M37" s="190">
         <v>0</v>
       </c>
-      <c r="N37" s="177"/>
-      <c r="O37" s="177"/>
-      <c r="P37" s="178"/>
-      <c r="Q37" s="166">
+      <c r="N37" s="191"/>
+      <c r="O37" s="191"/>
+      <c r="P37" s="192"/>
+      <c r="Q37" s="227">
         <v>0</v>
       </c>
-      <c r="R37" s="166"/>
-      <c r="S37" s="166"/>
-      <c r="T37" s="166">
+      <c r="R37" s="227"/>
+      <c r="S37" s="227"/>
+      <c r="T37" s="227">
         <v>0</v>
       </c>
-      <c r="U37" s="166"/>
-      <c r="V37" s="166"/>
-      <c r="W37" s="166">
+      <c r="U37" s="227"/>
+      <c r="V37" s="227"/>
+      <c r="W37" s="227">
         <v>0</v>
       </c>
-      <c r="X37" s="166"/>
-      <c r="Y37" s="166"/>
-      <c r="Z37" s="166">
+      <c r="X37" s="227"/>
+      <c r="Y37" s="227"/>
+      <c r="Z37" s="227">
         <v>0</v>
       </c>
-      <c r="AA37" s="166"/>
-      <c r="AB37" s="166"/>
-      <c r="AC37" s="170">
+      <c r="AA37" s="227"/>
+      <c r="AB37" s="227"/>
+      <c r="AC37" s="219">
         <v>0</v>
       </c>
-      <c r="AD37" s="171"/>
-      <c r="AE37" s="171"/>
-      <c r="AF37" s="171"/>
-      <c r="AG37" s="171"/>
-      <c r="AH37" s="172"/>
-      <c r="AI37" s="170">
+      <c r="AD37" s="220"/>
+      <c r="AE37" s="220"/>
+      <c r="AF37" s="220"/>
+      <c r="AG37" s="220"/>
+      <c r="AH37" s="221"/>
+      <c r="AI37" s="219">
         <v>0</v>
       </c>
-      <c r="AJ37" s="171"/>
-      <c r="AK37" s="171"/>
-      <c r="AL37" s="171"/>
-      <c r="AM37" s="171"/>
-      <c r="AN37" s="172"/>
+      <c r="AJ37" s="220"/>
+      <c r="AK37" s="220"/>
+      <c r="AL37" s="220"/>
+      <c r="AM37" s="220"/>
+      <c r="AN37" s="221"/>
       <c r="AO37">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -35832,7 +35832,7 @@
       </c>
     </row>
     <row r="38" spans="1:43" hidden="1">
-      <c r="A38" s="184"/>
+      <c r="A38" s="209"/>
       <c r="B38" s="46" t="s">
         <v>649</v>
       </c>
@@ -35840,64 +35840,64 @@
         <v>650</v>
       </c>
       <c r="D38" s="42"/>
-      <c r="E38" s="179">
+      <c r="E38" s="226">
         <v>100</v>
       </c>
-      <c r="F38" s="179"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="180">
+      <c r="F38" s="226"/>
+      <c r="G38" s="226"/>
+      <c r="H38" s="211">
         <v>0</v>
       </c>
-      <c r="I38" s="180"/>
-      <c r="J38" s="180"/>
-      <c r="K38" s="180">
+      <c r="I38" s="211"/>
+      <c r="J38" s="211"/>
+      <c r="K38" s="211">
         <v>0</v>
       </c>
-      <c r="L38" s="180"/>
-      <c r="M38" s="180"/>
-      <c r="N38" s="180">
+      <c r="L38" s="211"/>
+      <c r="M38" s="211"/>
+      <c r="N38" s="211">
         <v>0</v>
       </c>
-      <c r="O38" s="180"/>
-      <c r="P38" s="180"/>
-      <c r="Q38" s="165">
+      <c r="O38" s="211"/>
+      <c r="P38" s="211"/>
+      <c r="Q38" s="222">
         <v>50</v>
       </c>
-      <c r="R38" s="165"/>
-      <c r="S38" s="165"/>
-      <c r="T38" s="181">
+      <c r="R38" s="222"/>
+      <c r="S38" s="222"/>
+      <c r="T38" s="212">
         <v>85</v>
       </c>
-      <c r="U38" s="181"/>
-      <c r="V38" s="181"/>
-      <c r="W38" s="166">
+      <c r="U38" s="212"/>
+      <c r="V38" s="212"/>
+      <c r="W38" s="227">
         <v>3</v>
       </c>
-      <c r="X38" s="166"/>
-      <c r="Y38" s="166"/>
-      <c r="Z38" s="182">
+      <c r="X38" s="227"/>
+      <c r="Y38" s="227"/>
+      <c r="Z38" s="228">
         <v>100</v>
       </c>
-      <c r="AA38" s="182"/>
-      <c r="AB38" s="182"/>
-      <c r="AC38" s="167">
+      <c r="AA38" s="228"/>
+      <c r="AB38" s="228"/>
+      <c r="AC38" s="216">
         <v>50</v>
       </c>
-      <c r="AD38" s="168"/>
-      <c r="AE38" s="168"/>
-      <c r="AF38" s="169"/>
-      <c r="AG38" s="170">
+      <c r="AD38" s="217"/>
+      <c r="AE38" s="217"/>
+      <c r="AF38" s="218"/>
+      <c r="AG38" s="219">
         <v>0</v>
       </c>
-      <c r="AH38" s="171"/>
-      <c r="AI38" s="171"/>
-      <c r="AJ38" s="172"/>
-      <c r="AK38" s="167">
+      <c r="AH38" s="220"/>
+      <c r="AI38" s="220"/>
+      <c r="AJ38" s="221"/>
+      <c r="AK38" s="216">
         <v>50</v>
       </c>
-      <c r="AL38" s="168"/>
-      <c r="AM38" s="168"/>
-      <c r="AN38" s="169"/>
+      <c r="AL38" s="217"/>
+      <c r="AM38" s="217"/>
+      <c r="AN38" s="218"/>
       <c r="AO38">
         <f t="shared" si="0"/>
         <v>100</v>
@@ -35912,7 +35912,7 @@
       </c>
     </row>
     <row r="39" spans="1:43" hidden="1">
-      <c r="A39" s="184"/>
+      <c r="A39" s="209"/>
       <c r="B39" s="46" t="s">
         <v>651</v>
       </c>
@@ -35920,62 +35920,62 @@
         <v>652</v>
       </c>
       <c r="D39" s="42"/>
-      <c r="E39" s="173">
+      <c r="E39" s="166">
         <v>50</v>
       </c>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
-      <c r="H39" s="175"/>
-      <c r="I39" s="186">
+      <c r="F39" s="167"/>
+      <c r="G39" s="167"/>
+      <c r="H39" s="168"/>
+      <c r="I39" s="223">
         <v>100</v>
       </c>
-      <c r="J39" s="187"/>
-      <c r="K39" s="187"/>
-      <c r="L39" s="188"/>
-      <c r="M39" s="173">
+      <c r="J39" s="224"/>
+      <c r="K39" s="224"/>
+      <c r="L39" s="225"/>
+      <c r="M39" s="166">
         <v>50</v>
       </c>
-      <c r="N39" s="174"/>
-      <c r="O39" s="174"/>
-      <c r="P39" s="175"/>
-      <c r="Q39" s="181">
+      <c r="N39" s="167"/>
+      <c r="O39" s="167"/>
+      <c r="P39" s="168"/>
+      <c r="Q39" s="212">
         <v>85</v>
       </c>
-      <c r="R39" s="181"/>
-      <c r="S39" s="181"/>
-      <c r="T39" s="165">
+      <c r="R39" s="212"/>
+      <c r="S39" s="212"/>
+      <c r="T39" s="222">
         <v>50</v>
       </c>
-      <c r="U39" s="165"/>
-      <c r="V39" s="165"/>
-      <c r="W39" s="182">
+      <c r="U39" s="222"/>
+      <c r="V39" s="222"/>
+      <c r="W39" s="228">
         <v>100</v>
       </c>
-      <c r="X39" s="182"/>
-      <c r="Y39" s="182"/>
-      <c r="Z39" s="166">
+      <c r="X39" s="228"/>
+      <c r="Y39" s="228"/>
+      <c r="Z39" s="227">
         <v>0</v>
       </c>
-      <c r="AA39" s="166"/>
-      <c r="AB39" s="166"/>
-      <c r="AC39" s="170">
+      <c r="AA39" s="227"/>
+      <c r="AB39" s="227"/>
+      <c r="AC39" s="219">
         <v>0</v>
       </c>
-      <c r="AD39" s="171"/>
-      <c r="AE39" s="171"/>
-      <c r="AF39" s="172"/>
-      <c r="AG39" s="189">
+      <c r="AD39" s="220"/>
+      <c r="AE39" s="220"/>
+      <c r="AF39" s="221"/>
+      <c r="AG39" s="193">
         <v>15</v>
       </c>
-      <c r="AH39" s="190"/>
-      <c r="AI39" s="190"/>
-      <c r="AJ39" s="191"/>
-      <c r="AK39" s="170">
+      <c r="AH39" s="194"/>
+      <c r="AI39" s="194"/>
+      <c r="AJ39" s="195"/>
+      <c r="AK39" s="219">
         <v>0</v>
       </c>
-      <c r="AL39" s="171"/>
-      <c r="AM39" s="171"/>
-      <c r="AN39" s="172"/>
+      <c r="AL39" s="220"/>
+      <c r="AM39" s="220"/>
+      <c r="AN39" s="221"/>
       <c r="AO39">
         <f t="shared" si="0"/>
         <v>200</v>
@@ -35990,7 +35990,7 @@
       </c>
     </row>
     <row r="40" spans="1:43" hidden="1">
-      <c r="A40" s="184"/>
+      <c r="A40" s="209"/>
       <c r="B40" s="46" t="s">
         <v>653</v>
       </c>
@@ -35998,62 +35998,62 @@
         <v>654</v>
       </c>
       <c r="D40" s="42"/>
-      <c r="E40" s="173">
+      <c r="E40" s="166">
         <v>50</v>
       </c>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
-      <c r="H40" s="175"/>
-      <c r="I40" s="173">
+      <c r="F40" s="167"/>
+      <c r="G40" s="167"/>
+      <c r="H40" s="168"/>
+      <c r="I40" s="166">
         <v>50</v>
       </c>
-      <c r="J40" s="174"/>
-      <c r="K40" s="174"/>
-      <c r="L40" s="175"/>
-      <c r="M40" s="176">
+      <c r="J40" s="167"/>
+      <c r="K40" s="167"/>
+      <c r="L40" s="168"/>
+      <c r="M40" s="190">
         <v>0</v>
       </c>
-      <c r="N40" s="177"/>
-      <c r="O40" s="177"/>
-      <c r="P40" s="178"/>
-      <c r="Q40" s="165">
+      <c r="N40" s="191"/>
+      <c r="O40" s="191"/>
+      <c r="P40" s="192"/>
+      <c r="Q40" s="222">
         <v>50</v>
       </c>
-      <c r="R40" s="165"/>
-      <c r="S40" s="165"/>
-      <c r="T40" s="165">
+      <c r="R40" s="222"/>
+      <c r="S40" s="222"/>
+      <c r="T40" s="222">
         <v>50</v>
       </c>
-      <c r="U40" s="165"/>
-      <c r="V40" s="165"/>
-      <c r="W40" s="166">
+      <c r="U40" s="222"/>
+      <c r="V40" s="222"/>
+      <c r="W40" s="227">
         <v>0</v>
       </c>
-      <c r="X40" s="166"/>
-      <c r="Y40" s="166"/>
-      <c r="Z40" s="165">
+      <c r="X40" s="227"/>
+      <c r="Y40" s="227"/>
+      <c r="Z40" s="222">
         <v>50</v>
       </c>
-      <c r="AA40" s="165"/>
-      <c r="AB40" s="165"/>
-      <c r="AC40" s="170">
+      <c r="AA40" s="222"/>
+      <c r="AB40" s="222"/>
+      <c r="AC40" s="219">
         <v>0</v>
       </c>
-      <c r="AD40" s="171"/>
-      <c r="AE40" s="171"/>
-      <c r="AF40" s="172"/>
-      <c r="AG40" s="170">
+      <c r="AD40" s="220"/>
+      <c r="AE40" s="220"/>
+      <c r="AF40" s="221"/>
+      <c r="AG40" s="219">
         <v>0</v>
       </c>
-      <c r="AH40" s="171"/>
-      <c r="AI40" s="171"/>
-      <c r="AJ40" s="172"/>
-      <c r="AK40" s="170">
+      <c r="AH40" s="220"/>
+      <c r="AI40" s="220"/>
+      <c r="AJ40" s="221"/>
+      <c r="AK40" s="219">
         <v>0</v>
       </c>
-      <c r="AL40" s="171"/>
-      <c r="AM40" s="171"/>
-      <c r="AN40" s="172"/>
+      <c r="AL40" s="220"/>
+      <c r="AM40" s="220"/>
+      <c r="AN40" s="221"/>
       <c r="AO40">
         <f t="shared" si="0"/>
         <v>100</v>
@@ -36068,7 +36068,7 @@
       </c>
     </row>
     <row r="41" spans="1:43" hidden="1">
-      <c r="A41" s="185"/>
+      <c r="A41" s="210"/>
       <c r="B41" s="46" t="s">
         <v>655</v>
       </c>
@@ -36076,64 +36076,64 @@
         <v>656</v>
       </c>
       <c r="D41" s="42"/>
-      <c r="E41" s="179">
+      <c r="E41" s="226">
         <v>100</v>
       </c>
-      <c r="F41" s="179"/>
-      <c r="G41" s="179"/>
-      <c r="H41" s="181">
+      <c r="F41" s="226"/>
+      <c r="G41" s="226"/>
+      <c r="H41" s="212">
         <v>85</v>
       </c>
-      <c r="I41" s="181"/>
-      <c r="J41" s="181"/>
-      <c r="K41" s="181">
+      <c r="I41" s="212"/>
+      <c r="J41" s="212"/>
+      <c r="K41" s="212">
         <v>85</v>
       </c>
-      <c r="L41" s="181"/>
-      <c r="M41" s="181"/>
-      <c r="N41" s="181">
+      <c r="L41" s="212"/>
+      <c r="M41" s="212"/>
+      <c r="N41" s="212">
         <v>85</v>
       </c>
-      <c r="O41" s="181"/>
-      <c r="P41" s="181"/>
-      <c r="Q41" s="182">
+      <c r="O41" s="212"/>
+      <c r="P41" s="212"/>
+      <c r="Q41" s="228">
         <v>100</v>
       </c>
-      <c r="R41" s="182"/>
-      <c r="S41" s="182"/>
-      <c r="T41" s="181">
+      <c r="R41" s="228"/>
+      <c r="S41" s="228"/>
+      <c r="T41" s="212">
         <v>85</v>
       </c>
-      <c r="U41" s="181"/>
-      <c r="V41" s="181"/>
-      <c r="W41" s="165">
+      <c r="U41" s="212"/>
+      <c r="V41" s="212"/>
+      <c r="W41" s="222">
         <v>50</v>
       </c>
-      <c r="X41" s="165"/>
-      <c r="Y41" s="165"/>
-      <c r="Z41" s="166">
+      <c r="X41" s="222"/>
+      <c r="Y41" s="222"/>
+      <c r="Z41" s="227">
         <v>0</v>
       </c>
-      <c r="AA41" s="166"/>
-      <c r="AB41" s="166"/>
-      <c r="AC41" s="167">
+      <c r="AA41" s="227"/>
+      <c r="AB41" s="227"/>
+      <c r="AC41" s="216">
         <v>50</v>
       </c>
-      <c r="AD41" s="168"/>
-      <c r="AE41" s="168"/>
-      <c r="AF41" s="169"/>
-      <c r="AG41" s="167">
+      <c r="AD41" s="217"/>
+      <c r="AE41" s="217"/>
+      <c r="AF41" s="218"/>
+      <c r="AG41" s="216">
         <v>50</v>
       </c>
-      <c r="AH41" s="168"/>
-      <c r="AI41" s="168"/>
-      <c r="AJ41" s="169"/>
-      <c r="AK41" s="170">
+      <c r="AH41" s="217"/>
+      <c r="AI41" s="217"/>
+      <c r="AJ41" s="218"/>
+      <c r="AK41" s="219">
         <v>0</v>
       </c>
-      <c r="AL41" s="171"/>
-      <c r="AM41" s="171"/>
-      <c r="AN41" s="172"/>
+      <c r="AL41" s="220"/>
+      <c r="AM41" s="220"/>
+      <c r="AN41" s="221"/>
       <c r="AO41">
         <f t="shared" si="0"/>
         <v>355</v>
@@ -36150,6 +36150,310 @@
     <row r="42" spans="1:43" hidden="1"/>
   </sheetData>
   <mergeCells count="328">
+    <mergeCell ref="A1:AO1"/>
+    <mergeCell ref="W41:Y41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="AC41:AF41"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK41:AN41"/>
+    <mergeCell ref="AK39:AN39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="W40:Y40"/>
+    <mergeCell ref="Z40:AB40"/>
+    <mergeCell ref="AC40:AF40"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AK40:AN40"/>
+    <mergeCell ref="AI37:AN37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H38:J38"/>
+    <mergeCell ref="K38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="T38:V38"/>
+    <mergeCell ref="W38:Y38"/>
+    <mergeCell ref="Z38:AB38"/>
+    <mergeCell ref="AC38:AF38"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AK38:AN38"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AH37"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="W39:Y39"/>
+    <mergeCell ref="Z39:AB39"/>
+    <mergeCell ref="AC39:AF39"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="T41:V41"/>
+    <mergeCell ref="AK36:AN36"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T35:V35"/>
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="Z35:AB35"/>
+    <mergeCell ref="AC35:AF35"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H36:J36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="Q36:T36"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="Y36:AB36"/>
+    <mergeCell ref="AC36:AF36"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AC34:AH34"/>
+    <mergeCell ref="AI34:AN34"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AK35:AN35"/>
+    <mergeCell ref="AI31:AN31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="AC32:AH32"/>
+    <mergeCell ref="AI32:AN32"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="K33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T33:V33"/>
+    <mergeCell ref="W33:Y33"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="AC33:AF33"/>
+    <mergeCell ref="AG33:AJ33"/>
+    <mergeCell ref="AK33:AN33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="AI28:AN28"/>
+    <mergeCell ref="AG29:AJ29"/>
+    <mergeCell ref="AK29:AN29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="K30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="AC30:AH30"/>
+    <mergeCell ref="AI30:AN30"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AF29"/>
+    <mergeCell ref="AG26:AJ26"/>
+    <mergeCell ref="AK26:AN26"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="AC27:AH27"/>
+    <mergeCell ref="AI27:AN27"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AC26:AF26"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="AC28:AH28"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="AC31:AH31"/>
+    <mergeCell ref="AC18:AF18"/>
+    <mergeCell ref="AG18:AJ18"/>
+    <mergeCell ref="AK18:AN18"/>
+    <mergeCell ref="AC17:AF17"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="Z18:AB18"/>
+    <mergeCell ref="E25:P25"/>
+    <mergeCell ref="Q25:AB25"/>
+    <mergeCell ref="AC25:AN25"/>
+    <mergeCell ref="AK19:AN19"/>
+    <mergeCell ref="E2:P2"/>
+    <mergeCell ref="Q2:AB2"/>
+    <mergeCell ref="AC2:AN2"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="AG17:AJ17"/>
+    <mergeCell ref="AK17:AN17"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG16:AJ16"/>
+    <mergeCell ref="AK16:AN16"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="Z16:AB16"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="M8:P8"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="W15:Y15"/>
+    <mergeCell ref="Z15:AB15"/>
+    <mergeCell ref="W12:Y12"/>
+    <mergeCell ref="Z12:AB12"/>
+    <mergeCell ref="M11:P11"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="T14:V14"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="Z14:AB14"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="Q13:T13"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="Q9:T9"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="Q11:S11"/>
+    <mergeCell ref="T11:V11"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="Z17:AB17"/>
+    <mergeCell ref="W11:Y11"/>
+    <mergeCell ref="U9:X9"/>
+    <mergeCell ref="Z11:AB11"/>
+    <mergeCell ref="Q12:S12"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="Y3:AB3"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="Y4:AB4"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="Y5:AB5"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="W10:Y10"/>
+    <mergeCell ref="Y7:AB7"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="W6:Y6"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="U7:X7"/>
+    <mergeCell ref="Q8:T8"/>
+    <mergeCell ref="U8:X8"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="AG3:AJ3"/>
+    <mergeCell ref="AK3:AN3"/>
+    <mergeCell ref="AC6:AF6"/>
+    <mergeCell ref="AG6:AJ6"/>
+    <mergeCell ref="AK6:AN6"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AC5:AH5"/>
+    <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A14:A18"/>
@@ -36174,310 +36478,6 @@
     <mergeCell ref="AG12:AJ12"/>
     <mergeCell ref="AK12:AN12"/>
     <mergeCell ref="AC11:AH11"/>
-    <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="AG3:AJ3"/>
-    <mergeCell ref="AK3:AN3"/>
-    <mergeCell ref="AC6:AF6"/>
-    <mergeCell ref="AG6:AJ6"/>
-    <mergeCell ref="AK6:AN6"/>
-    <mergeCell ref="AC4:AH4"/>
-    <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="AC5:AH5"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="Y3:AB3"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="Y4:AB4"/>
-    <mergeCell ref="Q5:T5"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="Y5:AB5"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="Z10:AB10"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="W10:Y10"/>
-    <mergeCell ref="Y7:AB7"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="W6:Y6"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="Q7:T7"/>
-    <mergeCell ref="U7:X7"/>
-    <mergeCell ref="Q8:T8"/>
-    <mergeCell ref="U8:X8"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="Q11:S11"/>
-    <mergeCell ref="T11:V11"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="Z17:AB17"/>
-    <mergeCell ref="W11:Y11"/>
-    <mergeCell ref="U9:X9"/>
-    <mergeCell ref="Z11:AB11"/>
-    <mergeCell ref="Q12:S12"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="H12:J12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="Q13:T13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="Q9:T9"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="W15:Y15"/>
-    <mergeCell ref="Z15:AB15"/>
-    <mergeCell ref="W12:Y12"/>
-    <mergeCell ref="Z12:AB12"/>
-    <mergeCell ref="M11:P11"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="T14:V14"/>
-    <mergeCell ref="W14:Y14"/>
-    <mergeCell ref="Z14:AB14"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="M8:P8"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="E2:P2"/>
-    <mergeCell ref="Q2:AB2"/>
-    <mergeCell ref="AC2:AN2"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="AG17:AJ17"/>
-    <mergeCell ref="AK17:AN17"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG16:AJ16"/>
-    <mergeCell ref="AK16:AN16"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="W16:Y16"/>
-    <mergeCell ref="Z16:AB16"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="AC18:AF18"/>
-    <mergeCell ref="AG18:AJ18"/>
-    <mergeCell ref="AK18:AN18"/>
-    <mergeCell ref="AC17:AF17"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="Z18:AB18"/>
-    <mergeCell ref="E25:P25"/>
-    <mergeCell ref="Q25:AB25"/>
-    <mergeCell ref="AC25:AN25"/>
-    <mergeCell ref="AK19:AN19"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="K26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="Q26:T26"/>
-    <mergeCell ref="U26:X26"/>
-    <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AC26:AF26"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="Q28:T28"/>
-    <mergeCell ref="U28:X28"/>
-    <mergeCell ref="Y28:AB28"/>
-    <mergeCell ref="AC28:AH28"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="Y31:AB31"/>
-    <mergeCell ref="AC31:AH31"/>
-    <mergeCell ref="AG26:AJ26"/>
-    <mergeCell ref="AK26:AN26"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="K27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="Q27:T27"/>
-    <mergeCell ref="U27:X27"/>
-    <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="AC27:AH27"/>
-    <mergeCell ref="AI27:AN27"/>
-    <mergeCell ref="AI28:AN28"/>
-    <mergeCell ref="AG29:AJ29"/>
-    <mergeCell ref="AK29:AN29"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="K30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="AC30:AH30"/>
-    <mergeCell ref="AI30:AN30"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="K29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="T29:V29"/>
-    <mergeCell ref="W29:Y29"/>
-    <mergeCell ref="Z29:AB29"/>
-    <mergeCell ref="AC29:AF29"/>
-    <mergeCell ref="AI31:AN31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="K32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="Q32:T32"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="AC32:AH32"/>
-    <mergeCell ref="AI32:AN32"/>
-    <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="K33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="T33:V33"/>
-    <mergeCell ref="W33:Y33"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="AC33:AF33"/>
-    <mergeCell ref="AG33:AJ33"/>
-    <mergeCell ref="AK33:AN33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="T34:V34"/>
-    <mergeCell ref="W34:Y34"/>
-    <mergeCell ref="Z34:AB34"/>
-    <mergeCell ref="AC34:AH34"/>
-    <mergeCell ref="AI34:AN34"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AK35:AN35"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="K41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="T41:V41"/>
-    <mergeCell ref="AK36:AN36"/>
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="H35:J35"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="T35:V35"/>
-    <mergeCell ref="W35:Y35"/>
-    <mergeCell ref="Z35:AB35"/>
-    <mergeCell ref="AC35:AF35"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H36:J36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="Q36:T36"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="AC36:AF36"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="W38:Y38"/>
-    <mergeCell ref="Z38:AB38"/>
-    <mergeCell ref="AC38:AF38"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AK38:AN38"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="T37:V37"/>
-    <mergeCell ref="W37:Y37"/>
-    <mergeCell ref="Z37:AB37"/>
-    <mergeCell ref="AC37:AH37"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="T39:V39"/>
-    <mergeCell ref="W39:Y39"/>
-    <mergeCell ref="Z39:AB39"/>
-    <mergeCell ref="AC39:AF39"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="A1:AO1"/>
-    <mergeCell ref="W41:Y41"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="AC41:AF41"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK41:AN41"/>
-    <mergeCell ref="AK39:AN39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="T40:V40"/>
-    <mergeCell ref="W40:Y40"/>
-    <mergeCell ref="Z40:AB40"/>
-    <mergeCell ref="AC40:AF40"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AK40:AN40"/>
-    <mergeCell ref="AI37:AN37"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H38:J38"/>
-    <mergeCell ref="K38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="T38:V38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="AK19:AN19" location="Legend!A1" display="Legend" xr:uid="{A87F8DDE-5EE9-4FD3-8B7E-90C389B0AD3D}"/>
@@ -40482,7 +40482,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="229.5">
+    <row r="12" spans="1:15" ht="252" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>297</v>
       </c>
@@ -41154,6 +41154,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="dc4fa69f-dbc9-4bdf-b294-3e001048d319" xsi:nil="true"/>
@@ -41162,15 +41171,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41363,11 +41363,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B594BEB1-09E3-4FDF-B76F-D4DB5224F764}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A14187F6-9CDA-41BD-8F87-E97471BC2E2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A14187F6-9CDA-41BD-8F87-E97471BC2E2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B594BEB1-09E3-4FDF-B76F-D4DB5224F764}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
